--- a/ci-cd-merge-resolver/repoCollector/datasets/ruoyi-vue-pro.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/ruoyi-vue-pro.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="382">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,15 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>93d0bf5eada370ed32b43db0db13617cbe151909</t>
+  </si>
+  <si>
+    <t>199467a70d6ef7163c347c98ef73cb97e2b40eeb</t>
+  </si>
+  <si>
+    <t>e2edd7a49f3c9bb864ebd61c1656944bf541d168</t>
+  </si>
+  <si>
     <t>c80ffe437fe40ce641686a2f27a27337969bb462</t>
   </si>
   <si>
@@ -53,6 +62,15 @@
     <t>b167b419f4001be7ecbf544d25c6934f6bf0e2bf</t>
   </si>
   <si>
+    <t>ef26a1462efb8bbefd739e952152991abd191f1f</t>
+  </si>
+  <si>
+    <t>d3888d7b4ac9eddcf8cab1ac3787667af86b739b</t>
+  </si>
+  <si>
+    <t>896113bb404efb6f06012be04c2edc80f763cc62</t>
+  </si>
+  <si>
     <t>c4df87f7ee78eb2c060cb843ef19bb79828952b2</t>
   </si>
   <si>
@@ -62,22 +80,13 @@
     <t>f71ec384568d6291fef8216d0a6897c4395a9f70</t>
   </si>
   <si>
-    <t>93d0bf5eada370ed32b43db0db13617cbe151909</t>
-  </si>
-  <si>
-    <t>199467a70d6ef7163c347c98ef73cb97e2b40eeb</t>
-  </si>
-  <si>
-    <t>e2edd7a49f3c9bb864ebd61c1656944bf541d168</t>
-  </si>
-  <si>
-    <t>ef26a1462efb8bbefd739e952152991abd191f1f</t>
-  </si>
-  <si>
-    <t>d3888d7b4ac9eddcf8cab1ac3787667af86b739b</t>
-  </si>
-  <si>
-    <t>896113bb404efb6f06012be04c2edc80f763cc62</t>
+    <t>8939c042825471f6df4436d9991cdb1c7b0be95f</t>
+  </si>
+  <si>
+    <t>672db2c7d20bf453c9483430d822f6f913970375</t>
+  </si>
+  <si>
+    <t>8ffe9272e80ec9b07fce6b29d8f041bc5ac7a01b</t>
   </si>
   <si>
     <t>b208f100a68c22148c7d16606430eb76a2e41c94</t>
@@ -89,13 +98,187 @@
     <t>b8889a94c7185f1097d65c4a94bcfa93df784a11</t>
   </si>
   <si>
-    <t>8939c042825471f6df4436d9991cdb1c7b0be95f</t>
-  </si>
-  <si>
-    <t>672db2c7d20bf453c9483430d822f6f913970375</t>
-  </si>
-  <si>
-    <t>8ffe9272e80ec9b07fce6b29d8f041bc5ac7a01b</t>
+    <t>269c1fdabf7533250c030c773fa5db0ac0d55051</t>
+  </si>
+  <si>
+    <t>a3bbfe6ccaf76a36cbe780b6bea9f30cdae428c7</t>
+  </si>
+  <si>
+    <t>ecda40d300db4c6559fe817a6a6b46a19e7713b1</t>
+  </si>
+  <si>
+    <t>455a01264445eb3d48f417f7a2bb1f57d35eba58</t>
+  </si>
+  <si>
+    <t>5573ce20db11f8da8571f4aa1526d0d2265b7e86</t>
+  </si>
+  <si>
+    <t>568216084e83e0dcb6f299c42f6977953035afa0</t>
+  </si>
+  <si>
+    <t>863ec14f0b5ddf13cf3402029d5aef1829048907</t>
+  </si>
+  <si>
+    <t>7a8e91345ff18b3d29085ad8b8ede0e88dacd543</t>
+  </si>
+  <si>
+    <t>e79005a0a0a88dff1a7c89af5d6403af222d487e</t>
+  </si>
+  <si>
+    <t>53d5c394b6979dac4cfe74eb816a1ca9e98c55eb</t>
+  </si>
+  <si>
+    <t>0f9cf91899050d109105f8e5a8c53c39db35e6da</t>
+  </si>
+  <si>
+    <t>3a07bcc3c663f843ef130cff616df5a9ccb96902</t>
+  </si>
+  <si>
+    <t>a000048196d9983177f0da0ec3c9e6565664bd28</t>
+  </si>
+  <si>
+    <t>2273d72f52788c9d0900febd9337bb15aa8d30cb</t>
+  </si>
+  <si>
+    <t>0fbffdc1d38e820f220127eba23ee56d810cdf43</t>
+  </si>
+  <si>
+    <t>adece67532cafa1f16278764d22f9aa9dc81b534</t>
+  </si>
+  <si>
+    <t>7a8c37d7ac95ef8b11d7072189c970f2f9c0e776</t>
+  </si>
+  <si>
+    <t>ea5b12f21e2c0eb3e9e833b12e1af3bfad0681f1</t>
+  </si>
+  <si>
+    <t>4d5e501a41e4d6dcd9ad28d17763ab126f274b5b</t>
+  </si>
+  <si>
+    <t>876659b01d20f95b6e77f6b6ff1c8ac26156922f</t>
+  </si>
+  <si>
+    <t>569ff42e6f9d2a4499ca0cfe113585e705ab59f2</t>
+  </si>
+  <si>
+    <t>e1bac0818fd040c62f9b3b81f330e825526008ce</t>
+  </si>
+  <si>
+    <t>2ee2a2829219de2e6d6da270d02c836a22c3d94f</t>
+  </si>
+  <si>
+    <t>86de4684133b1da6e09e1307357418949f5c015c</t>
+  </si>
+  <si>
+    <t>a39647efc072098b26ec79e87dff63ba9a0c6c8a</t>
+  </si>
+  <si>
+    <t>f3ef0e72e2cbe7fad8b368ec3aef998e643a6df2</t>
+  </si>
+  <si>
+    <t>853afd218479ee0630cb8c52a399ce4e133ee258</t>
+  </si>
+  <si>
+    <t>342b1ab7bfa6965642db83a9bb04f8695069abfc</t>
+  </si>
+  <si>
+    <t>17ec78f68a5a1eae7a985d7a1c207cf6a517e912</t>
+  </si>
+  <si>
+    <t>7c150f080c736176b321ba84c37f58455682e5cf</t>
+  </si>
+  <si>
+    <t>769302cec52d63c3403923fff60780b81b336b70</t>
+  </si>
+  <si>
+    <t>97ae1766e8f1d291781f62f25fb76ca5cc16c268</t>
+  </si>
+  <si>
+    <t>8508bb4d92db8f6152d627c48b3f43d5af28f99c</t>
+  </si>
+  <si>
+    <t>7db87c45a8859140535b639bee4ab23c24ca7aa6</t>
+  </si>
+  <si>
+    <t>3e6ab43704027fdf1e6916377da5ba596f8dce98</t>
+  </si>
+  <si>
+    <t>f38485ffd501e51d5a935482f824d363faee2de4</t>
+  </si>
+  <si>
+    <t>9dec02d02ec0721481392e3774be8131d2dc26e8</t>
+  </si>
+  <si>
+    <t>03d3ebdf05f2f95c68b7e25c1e4d5b46d373ee52</t>
+  </si>
+  <si>
+    <t>828901991da4e07abeb67051c372b9ca9ebb1d07</t>
+  </si>
+  <si>
+    <t>9c2243419b2974f27c99679bc1f29203a062490a</t>
+  </si>
+  <si>
+    <t>a1164f24e0434fee7f72f13b623041b7866e45b4</t>
+  </si>
+  <si>
+    <t>e633c7cfe3f350cc942c51463ae316a4214481f1</t>
+  </si>
+  <si>
+    <t>e6fcb603325f17af859481d0ef6591592233b209</t>
+  </si>
+  <si>
+    <t>a34de9f2239cedfcba3ff189c76df36bb6c7b615</t>
+  </si>
+  <si>
+    <t>f3b680cfd317ae6805400996d67360c5e138e129</t>
+  </si>
+  <si>
+    <t>89ca20e298933ab8aec87ad8c83ffd941736fc63</t>
+  </si>
+  <si>
+    <t>d4ed2c49f18a4258d141fe289245d279b6c89b3e</t>
+  </si>
+  <si>
+    <t>a557f0733f89ebd7c9a9b6259d3ba09a2e49a8f1</t>
+  </si>
+  <si>
+    <t>74490ed03bcddc551262b497af95f3ef92f9a557</t>
+  </si>
+  <si>
+    <t>c2db16cc152dc42e5f3293219083407a1d08b7ff</t>
+  </si>
+  <si>
+    <t>6aba222d9e9fd160f8758de6f9ce5dfd3ceeaaff</t>
+  </si>
+  <si>
+    <t>8156e44f317c0d6e342dc7a92fd9d770d8de43c2</t>
+  </si>
+  <si>
+    <t>4fed75935fa76a68aa8008765928a7cb08d8b2fb</t>
+  </si>
+  <si>
+    <t>8e0398bce67fd3f7537065928af6a09229e3e0cb</t>
+  </si>
+  <si>
+    <t>0ff319ebf7cd53e0545c04ae9bf2eb074f1312d5</t>
+  </si>
+  <si>
+    <t>be86cdfd517d65fcaf513f1f6b6daf11d5f12533</t>
+  </si>
+  <si>
+    <t>5d456f1336895c186cb16fe5585fac2d1b224215</t>
+  </si>
+  <si>
+    <t>fa65a6e1d07d53e982b643aeff4319d663948053</t>
+  </si>
+  <si>
+    <t>5d43f050497076b9b1b2552c053aedd5c39252d7</t>
+  </si>
+  <si>
+    <t>759f752db56e721c639a4e94a16988ab0a4568c8</t>
+  </si>
+  <si>
+    <t>1efe2e74b78a676e962aa75a4671e3d0d46e1277</t>
   </si>
   <si>
     <t>5f993c6a9fb75887f751531c30a1041c4815e215</t>
@@ -107,40 +290,10 @@
     <t>dace9cfed56fe01db443d787e605ac4026c20235</t>
   </si>
   <si>
-    <t>269c1fdabf7533250c030c773fa5db0ac0d55051</t>
-  </si>
-  <si>
-    <t>a3bbfe6ccaf76a36cbe780b6bea9f30cdae428c7</t>
-  </si>
-  <si>
-    <t>ecda40d300db4c6559fe817a6a6b46a19e7713b1</t>
-  </si>
-  <si>
-    <t>455a01264445eb3d48f417f7a2bb1f57d35eba58</t>
-  </si>
-  <si>
-    <t>5573ce20db11f8da8571f4aa1526d0d2265b7e86</t>
-  </si>
-  <si>
-    <t>568216084e83e0dcb6f299c42f6977953035afa0</t>
-  </si>
-  <si>
-    <t>f38485ffd501e51d5a935482f824d363faee2de4</t>
-  </si>
-  <si>
-    <t>9dec02d02ec0721481392e3774be8131d2dc26e8</t>
-  </si>
-  <si>
-    <t>03d3ebdf05f2f95c68b7e25c1e4d5b46d373ee52</t>
-  </si>
-  <si>
-    <t>f3b680cfd317ae6805400996d67360c5e138e129</t>
-  </si>
-  <si>
-    <t>89ca20e298933ab8aec87ad8c83ffd941736fc63</t>
-  </si>
-  <si>
-    <t>d4ed2c49f18a4258d141fe289245d279b6c89b3e</t>
+    <t>283c1009a43940f740f9a7a8d97b1429543f7ab8</t>
+  </si>
+  <si>
+    <t>c92fa0685c6c63ec665f0b708a83c17133a4e9d7</t>
   </si>
   <si>
     <t>83537fd2d9b8e9561a5cdb9764458ba11907048e</t>
@@ -149,70 +302,34 @@
     <t>9a3a56130d36493269ebbe8e14150fcaf7bdcfdb</t>
   </si>
   <si>
-    <t>3a07bcc3c663f843ef130cff616df5a9ccb96902</t>
-  </si>
-  <si>
-    <t>adece67532cafa1f16278764d22f9aa9dc81b534</t>
-  </si>
-  <si>
-    <t>7a8c37d7ac95ef8b11d7072189c970f2f9c0e776</t>
-  </si>
-  <si>
-    <t>ea5b12f21e2c0eb3e9e833b12e1af3bfad0681f1</t>
-  </si>
-  <si>
-    <t>863ec14f0b5ddf13cf3402029d5aef1829048907</t>
-  </si>
-  <si>
-    <t>7a8e91345ff18b3d29085ad8b8ede0e88dacd543</t>
-  </si>
-  <si>
-    <t>e79005a0a0a88dff1a7c89af5d6403af222d487e</t>
-  </si>
-  <si>
-    <t>4d5e501a41e4d6dcd9ad28d17763ab126f274b5b</t>
-  </si>
-  <si>
-    <t>876659b01d20f95b6e77f6b6ff1c8ac26156922f</t>
-  </si>
-  <si>
-    <t>569ff42e6f9d2a4499ca0cfe113585e705ab59f2</t>
-  </si>
-  <si>
-    <t>a000048196d9983177f0da0ec3c9e6565664bd28</t>
-  </si>
-  <si>
-    <t>2273d72f52788c9d0900febd9337bb15aa8d30cb</t>
-  </si>
-  <si>
-    <t>0fbffdc1d38e820f220127eba23ee56d810cdf43</t>
-  </si>
-  <si>
-    <t>6aba222d9e9fd160f8758de6f9ce5dfd3ceeaaff</t>
-  </si>
-  <si>
-    <t>8156e44f317c0d6e342dc7a92fd9d770d8de43c2</t>
-  </si>
-  <si>
-    <t>4fed75935fa76a68aa8008765928a7cb08d8b2fb</t>
-  </si>
-  <si>
-    <t>a557f0733f89ebd7c9a9b6259d3ba09a2e49a8f1</t>
-  </si>
-  <si>
-    <t>74490ed03bcddc551262b497af95f3ef92f9a557</t>
-  </si>
-  <si>
-    <t>c2db16cc152dc42e5f3293219083407a1d08b7ff</t>
-  </si>
-  <si>
-    <t>5d43f050497076b9b1b2552c053aedd5c39252d7</t>
-  </si>
-  <si>
-    <t>759f752db56e721c639a4e94a16988ab0a4568c8</t>
-  </si>
-  <si>
-    <t>1efe2e74b78a676e962aa75a4671e3d0d46e1277</t>
+    <t>485a70de6dc97914d532c6ba76c1c190afd5a9f4</t>
+  </si>
+  <si>
+    <t>4ebbe4dd355286b3c88890af0c969e9b72dc1d42</t>
+  </si>
+  <si>
+    <t>2769f774a08f9f571ff57018a93133d95e1f46b8</t>
+  </si>
+  <si>
+    <t>ec2bca7331ee24ba3315c97d02240eb0ebca8da4</t>
+  </si>
+  <si>
+    <t>b535716084d5f2c6dc7702fd964fb969d7511a1d</t>
+  </si>
+  <si>
+    <t>8cef02613de82527e14522bb22c8ef3580c8cba0</t>
+  </si>
+  <si>
+    <t>28965b9bbf5d5606f2b4762d09d1f3dd2f3af74f</t>
+  </si>
+  <si>
+    <t>a1cb21f3b1daa9a6bb74e6cab64afdd231376251</t>
+  </si>
+  <si>
+    <t>32758bc4c1b47f79161dd13124c53dced29afeda</t>
+  </si>
+  <si>
+    <t>65b811479981963bdf0ed5709e1c60387dbf3fae</t>
   </si>
   <si>
     <t>1dc5fd2c24499cb123b8cad26fb5804ee42df0f0</t>
@@ -224,54 +341,6 @@
     <t>c2f9bad3ad745713a665b718501cb7b3c75922ce</t>
   </si>
   <si>
-    <t>a1cb21f3b1daa9a6bb74e6cab64afdd231376251</t>
-  </si>
-  <si>
-    <t>32758bc4c1b47f79161dd13124c53dced29afeda</t>
-  </si>
-  <si>
-    <t>65b811479981963bdf0ed5709e1c60387dbf3fae</t>
-  </si>
-  <si>
-    <t>e633c7cfe3f350cc942c51463ae316a4214481f1</t>
-  </si>
-  <si>
-    <t>e6fcb603325f17af859481d0ef6591592233b209</t>
-  </si>
-  <si>
-    <t>a34de9f2239cedfcba3ff189c76df36bb6c7b615</t>
-  </si>
-  <si>
-    <t>53d5c394b6979dac4cfe74eb816a1ca9e98c55eb</t>
-  </si>
-  <si>
-    <t>0f9cf91899050d109105f8e5a8c53c39db35e6da</t>
-  </si>
-  <si>
-    <t>8e0398bce67fd3f7537065928af6a09229e3e0cb</t>
-  </si>
-  <si>
-    <t>0ff319ebf7cd53e0545c04ae9bf2eb074f1312d5</t>
-  </si>
-  <si>
-    <t>be86cdfd517d65fcaf513f1f6b6daf11d5f12533</t>
-  </si>
-  <si>
-    <t>828901991da4e07abeb67051c372b9ca9ebb1d07</t>
-  </si>
-  <si>
-    <t>9c2243419b2974f27c99679bc1f29203a062490a</t>
-  </si>
-  <si>
-    <t>a1164f24e0434fee7f72f13b623041b7866e45b4</t>
-  </si>
-  <si>
-    <t>283c1009a43940f740f9a7a8d97b1429543f7ab8</t>
-  </si>
-  <si>
-    <t>c92fa0685c6c63ec665f0b708a83c17133a4e9d7</t>
-  </si>
-  <si>
     <t>e86be20a8e9fa29fd686899b17d366e81b9bf735</t>
   </si>
   <si>
@@ -281,49 +350,94 @@
     <t>661c55cb493236a4846966ece4ac9d9deb93ec37</t>
   </si>
   <si>
-    <t>485a70de6dc97914d532c6ba76c1c190afd5a9f4</t>
-  </si>
-  <si>
-    <t>2769f774a08f9f571ff57018a93133d95e1f46b8</t>
-  </si>
-  <si>
-    <t>ec2bca7331ee24ba3315c97d02240eb0ebca8da4</t>
-  </si>
-  <si>
-    <t>b535716084d5f2c6dc7702fd964fb969d7511a1d</t>
-  </si>
-  <si>
-    <t>8cef02613de82527e14522bb22c8ef3580c8cba0</t>
-  </si>
-  <si>
-    <t>28965b9bbf5d5606f2b4762d09d1f3dd2f3af74f</t>
-  </si>
-  <si>
-    <t>e1bac0818fd040c62f9b3b81f330e825526008ce</t>
-  </si>
-  <si>
-    <t>2ee2a2829219de2e6d6da270d02c836a22c3d94f</t>
-  </si>
-  <si>
-    <t>86de4684133b1da6e09e1307357418949f5c015c</t>
-  </si>
-  <si>
-    <t>5d456f1336895c186cb16fe5585fac2d1b224215</t>
-  </si>
-  <si>
-    <t>fa65a6e1d07d53e982b643aeff4319d663948053</t>
-  </si>
-  <si>
-    <t>8508bb4d92db8f6152d627c48b3f43d5af28f99c</t>
-  </si>
-  <si>
-    <t>7db87c45a8859140535b639bee4ab23c24ca7aa6</t>
-  </si>
-  <si>
-    <t>3e6ab43704027fdf1e6916377da5ba596f8dce98</t>
-  </si>
-  <si>
-    <t>4ebbe4dd355286b3c88890af0c969e9b72dc1d42</t>
+    <t>7d867909d7f12714f7126602871254dacb39527b</t>
+  </si>
+  <si>
+    <t>f153406146c8ee8257ee9356245b969e81b6a625</t>
+  </si>
+  <si>
+    <t>ed3b6703baf5518e944fa4425754357d6889fabd</t>
+  </si>
+  <si>
+    <t>e7ad73c27855e36e2cd1bd2c0f809ea6654f4ea8</t>
+  </si>
+  <si>
+    <t>b0472743069bcb35e30cad0e6fd1ba8933b2a564</t>
+  </si>
+  <si>
+    <t>d7656535a2eab25ad306007e7a3ae3908f6e731f</t>
+  </si>
+  <si>
+    <t>ab8cad2352e2d46cf7f08b4ad14322e504b4e163</t>
+  </si>
+  <si>
+    <t>61edbcb9ceab479ad67189077e1dfcbf87f8bf24</t>
+  </si>
+  <si>
+    <t>bbc59e44d0e6623c8de2aeb77c851c68d5aecb2b</t>
+  </si>
+  <si>
+    <t>7609c74c8b3a7b09cf1aec089f5e31bed3f7e433</t>
+  </si>
+  <si>
+    <t>bba36bfca9d720b55eb65757ba9da08eec0fdeb9</t>
+  </si>
+  <si>
+    <t>d597d0057ee9d4e5e3ffbc89604bb324c3c5ca7e</t>
+  </si>
+  <si>
+    <t>efc535c05153d53123e6d7d5cb456a140f66d91f</t>
+  </si>
+  <si>
+    <t>8eb76c210db93b79d6fb0ffe2b706fc8fee4e79c</t>
+  </si>
+  <si>
+    <t>50e31f1bec9686e94b1c4b8b5eace76151635815</t>
+  </si>
+  <si>
+    <t>eefd5341b34057f07b603f5bc2a3d4d6e261d4bc</t>
+  </si>
+  <si>
+    <t>ff32b015abfe91fcb11a72b52d88f05717d81868</t>
+  </si>
+  <si>
+    <t>8fb018a69984102f721a7323c7a398e2267253ee</t>
+  </si>
+  <si>
+    <t>c320b525b5c2945f6c9f7b4787763a12d32f1432</t>
+  </si>
+  <si>
+    <t>b9ffa1820dcaa20b4e8741b4dc5d02d8f03473e0</t>
+  </si>
+  <si>
+    <t>0c68962a97c9910c86de5a66ba4c4e7f688fe78f</t>
+  </si>
+  <si>
+    <t>3682bcda3e90649007a97477dbbbb3da40765ad5</t>
+  </si>
+  <si>
+    <t>599c432abb1e4629fe746db2c47c9b0a37e2fc90</t>
+  </si>
+  <si>
+    <t>06634a426584d663a58c57b35c9aaffbd9757810</t>
+  </si>
+  <si>
+    <t>28c818e9bcbb62eec212b417e059bdb480ade30e</t>
+  </si>
+  <si>
+    <t>ed920f3fd3df8c5d11dd5880cffb99a528de4559</t>
+  </si>
+  <si>
+    <t>4fb4af2c5c9854db57d9244a941671308f695bb9</t>
+  </si>
+  <si>
+    <t>d8451b004edacb1322948bc63842c5d5e417a48e</t>
+  </si>
+  <si>
+    <t>7f8261ce37fe1b4665109ccc05c0a4dcc85394e5</t>
+  </si>
+  <si>
+    <t>f6601ab6390a9a36facec8df78cecb2ccfdf557d</t>
   </si>
   <si>
     <t>4ed753d6b8d59683fb551793ac268fb9560d4e4a</t>
@@ -335,67 +449,13 @@
     <t>fd2d067324b8d0135758f2d9b9e2075210b914ce</t>
   </si>
   <si>
-    <t>efc535c05153d53123e6d7d5cb456a140f66d91f</t>
-  </si>
-  <si>
-    <t>8eb76c210db93b79d6fb0ffe2b706fc8fee4e79c</t>
-  </si>
-  <si>
-    <t>50e31f1bec9686e94b1c4b8b5eace76151635815</t>
-  </si>
-  <si>
-    <t>d8451b004edacb1322948bc63842c5d5e417a48e</t>
-  </si>
-  <si>
-    <t>7f8261ce37fe1b4665109ccc05c0a4dcc85394e5</t>
-  </si>
-  <si>
-    <t>f6601ab6390a9a36facec8df78cecb2ccfdf557d</t>
-  </si>
-  <si>
-    <t>7d867909d7f12714f7126602871254dacb39527b</t>
-  </si>
-  <si>
-    <t>f153406146c8ee8257ee9356245b969e81b6a625</t>
-  </si>
-  <si>
-    <t>ed3b6703baf5518e944fa4425754357d6889fabd</t>
-  </si>
-  <si>
-    <t>3682bcda3e90649007a97477dbbbb3da40765ad5</t>
-  </si>
-  <si>
-    <t>599c432abb1e4629fe746db2c47c9b0a37e2fc90</t>
-  </si>
-  <si>
-    <t>06634a426584d663a58c57b35c9aaffbd9757810</t>
-  </si>
-  <si>
-    <t>e7ad73c27855e36e2cd1bd2c0f809ea6654f4ea8</t>
-  </si>
-  <si>
-    <t>b0472743069bcb35e30cad0e6fd1ba8933b2a564</t>
-  </si>
-  <si>
-    <t>d7656535a2eab25ad306007e7a3ae3908f6e731f</t>
-  </si>
-  <si>
-    <t>28c818e9bcbb62eec212b417e059bdb480ade30e</t>
-  </si>
-  <si>
-    <t>ed920f3fd3df8c5d11dd5880cffb99a528de4559</t>
-  </si>
-  <si>
-    <t>4fb4af2c5c9854db57d9244a941671308f695bb9</t>
-  </si>
-  <si>
-    <t>7609c74c8b3a7b09cf1aec089f5e31bed3f7e433</t>
-  </si>
-  <si>
-    <t>bba36bfca9d720b55eb65757ba9da08eec0fdeb9</t>
-  </si>
-  <si>
-    <t>d597d0057ee9d4e5e3ffbc89604bb324c3c5ca7e</t>
+    <t>0f4f5b484b0dc72903e76cfb1c8f9da0e3007f58</t>
+  </si>
+  <si>
+    <t>7119350a37d09ae31380119ca49f741e8b059398</t>
+  </si>
+  <si>
+    <t>6639d371328a51bdc70ea43e09d74f35f3d6af0e</t>
   </si>
   <si>
     <t>41640642d44b65559dab536676d90689299a245e</t>
@@ -407,13 +467,46 @@
     <t>a8d7da329f35bbd410fa3ea793cea8482467fe9f</t>
   </si>
   <si>
-    <t>c320b525b5c2945f6c9f7b4787763a12d32f1432</t>
-  </si>
-  <si>
-    <t>b9ffa1820dcaa20b4e8741b4dc5d02d8f03473e0</t>
-  </si>
-  <si>
-    <t>0c68962a97c9910c86de5a66ba4c4e7f688fe78f</t>
+    <t>7da7c10b4722fc15677a9c92aca589a4211aacdc</t>
+  </si>
+  <si>
+    <t>6e89d33d393709e8c94258765b427d6aa9f26b18</t>
+  </si>
+  <si>
+    <t>367e3b9880eb9e3e0f7f427ffe8c6e6f4e186f1e</t>
+  </si>
+  <si>
+    <t>c97fafebbe3f23bd124b991983cef5484ca477d3</t>
+  </si>
+  <si>
+    <t>f7c56ad4ebba4eed76d93733f1712a7b07d214f1</t>
+  </si>
+  <si>
+    <t>4c9777c8d4864e5c6502a50c41e8c380f0357a3c</t>
+  </si>
+  <si>
+    <t>aab61f79631d1381cb2d4f40b68ea8282f077406</t>
+  </si>
+  <si>
+    <t>534c64709fc6c9d6053f1f898d62438877ab4bef</t>
+  </si>
+  <si>
+    <t>a44a45a2cbd3c68a6307b0df7654a6b67ea8ad33</t>
+  </si>
+  <si>
+    <t>38c24bddb692b526c5bc3add8320f7f7cf99dd69</t>
+  </si>
+  <si>
+    <t>cf7ff1ca8ab8d15e76885cc7424f5588caaa3160</t>
+  </si>
+  <si>
+    <t>149cab1dac170df649be1c0d08e446b58bb42a11</t>
+  </si>
+  <si>
+    <t>c2789f628c2c053b50986d25de057cb2efcc6953</t>
+  </si>
+  <si>
+    <t>24261cf767fea0e71d813e590e12d3debb7b97db</t>
   </si>
   <si>
     <t>bb798681f778ff9e5906d2a2bb73a436b624888b</t>
@@ -425,40 +518,31 @@
     <t>0e07da807a266cf98af18ea4c98023f7e66904d6</t>
   </si>
   <si>
-    <t>ab8cad2352e2d46cf7f08b4ad14322e504b4e163</t>
-  </si>
-  <si>
-    <t>61edbcb9ceab479ad67189077e1dfcbf87f8bf24</t>
-  </si>
-  <si>
-    <t>bbc59e44d0e6623c8de2aeb77c851c68d5aecb2b</t>
-  </si>
-  <si>
-    <t>a44a45a2cbd3c68a6307b0df7654a6b67ea8ad33</t>
-  </si>
-  <si>
-    <t>38c24bddb692b526c5bc3add8320f7f7cf99dd69</t>
-  </si>
-  <si>
-    <t>cf7ff1ca8ab8d15e76885cc7424f5588caaa3160</t>
-  </si>
-  <si>
-    <t>c97fafebbe3f23bd124b991983cef5484ca477d3</t>
-  </si>
-  <si>
-    <t>f7c56ad4ebba4eed76d93733f1712a7b07d214f1</t>
-  </si>
-  <si>
-    <t>4c9777c8d4864e5c6502a50c41e8c380f0357a3c</t>
-  </si>
-  <si>
-    <t>0f4f5b484b0dc72903e76cfb1c8f9da0e3007f58</t>
-  </si>
-  <si>
-    <t>7119350a37d09ae31380119ca49f741e8b059398</t>
-  </si>
-  <si>
-    <t>6639d371328a51bdc70ea43e09d74f35f3d6af0e</t>
+    <t>8c681a77f5170ddb39f6fe6f4605ecceb06e3de0</t>
+  </si>
+  <si>
+    <t>3f8221ba845420160107cfedac30745751e3fb69</t>
+  </si>
+  <si>
+    <t>254b55778f839de4639c4831ca0110f89bbbaf36</t>
+  </si>
+  <si>
+    <t>8236154ae8ead0422dbfc776cc285081800bc33b</t>
+  </si>
+  <si>
+    <t>a364153d4a9a34375151d8527a5ad54ed60f6c22</t>
+  </si>
+  <si>
+    <t>b8e56a6bde19e74a1d2682a134e7811fbdabed1f</t>
+  </si>
+  <si>
+    <t>3f1cd8057399e8a12c9d25da588ff04571e10374</t>
+  </si>
+  <si>
+    <t>5e31062d6b64ff7c007f332040c4a805a5441410</t>
+  </si>
+  <si>
+    <t>197c4ad9bf159f6f3f08bf07cbdd14001f1e8b16</t>
   </si>
   <si>
     <t>9f8c6a944c80afa3b60b547d5eb92afc7c288d80</t>
@@ -470,55 +554,31 @@
     <t>4cefea68809b5ca38903c6254357ac985b974810</t>
   </si>
   <si>
-    <t>7da7c10b4722fc15677a9c92aca589a4211aacdc</t>
-  </si>
-  <si>
-    <t>6e89d33d393709e8c94258765b427d6aa9f26b18</t>
-  </si>
-  <si>
-    <t>367e3b9880eb9e3e0f7f427ffe8c6e6f4e186f1e</t>
-  </si>
-  <si>
-    <t>eefd5341b34057f07b603f5bc2a3d4d6e261d4bc</t>
-  </si>
-  <si>
-    <t>ff32b015abfe91fcb11a72b52d88f05717d81868</t>
-  </si>
-  <si>
-    <t>8fb018a69984102f721a7323c7a398e2267253ee</t>
-  </si>
-  <si>
-    <t>3f1cd8057399e8a12c9d25da588ff04571e10374</t>
-  </si>
-  <si>
-    <t>5e31062d6b64ff7c007f332040c4a805a5441410</t>
-  </si>
-  <si>
-    <t>197c4ad9bf159f6f3f08bf07cbdd14001f1e8b16</t>
-  </si>
-  <si>
-    <t>aab61f79631d1381cb2d4f40b68ea8282f077406</t>
-  </si>
-  <si>
-    <t>534c64709fc6c9d6053f1f898d62438877ab4bef</t>
-  </si>
-  <si>
-    <t>8c681a77f5170ddb39f6fe6f4605ecceb06e3de0</t>
-  </si>
-  <si>
-    <t>3f8221ba845420160107cfedac30745751e3fb69</t>
-  </si>
-  <si>
-    <t>254b55778f839de4639c4831ca0110f89bbbaf36</t>
-  </si>
-  <si>
-    <t>8236154ae8ead0422dbfc776cc285081800bc33b</t>
-  </si>
-  <si>
-    <t>a364153d4a9a34375151d8527a5ad54ed60f6c22</t>
-  </si>
-  <si>
-    <t>b8e56a6bde19e74a1d2682a134e7811fbdabed1f</t>
+    <t>735ec9e3ac354172cc406eb782336bdcf677ce98</t>
+  </si>
+  <si>
+    <t>d33afd7a9a843a353eb29f5c59a1a6ecae91172e</t>
+  </si>
+  <si>
+    <t>4b09bff64b3aad5ddd945df8b6dc3c1cf1fd9010</t>
+  </si>
+  <si>
+    <t>3871a1f83fe9f3059ce4c5510cea63c7346c143a</t>
+  </si>
+  <si>
+    <t>266e892a9e7102b2541374a4a283b9f6e012af49</t>
+  </si>
+  <si>
+    <t>46c825cb6f1efe399d339144749ed5f0c95b0314</t>
+  </si>
+  <si>
+    <t>f1d887d0e0755c09372e19ed524719357115be9f</t>
+  </si>
+  <si>
+    <t>d9dda54ccedb9dbf9ea13dc1190f95a136f55db5</t>
+  </si>
+  <si>
+    <t>deab8c1cc6bb7864d9c40e0c369f649f6f9bfa41</t>
   </si>
   <si>
     <t>e7999749fb72e1bd8c8568ab2d4265a2531efe36</t>
@@ -530,33 +590,6 @@
     <t>916024b8914482eb6b4e32f52e75b4193aa4e108</t>
   </si>
   <si>
-    <t>f1d887d0e0755c09372e19ed524719357115be9f</t>
-  </si>
-  <si>
-    <t>d9dda54ccedb9dbf9ea13dc1190f95a136f55db5</t>
-  </si>
-  <si>
-    <t>deab8c1cc6bb7864d9c40e0c369f649f6f9bfa41</t>
-  </si>
-  <si>
-    <t>3871a1f83fe9f3059ce4c5510cea63c7346c143a</t>
-  </si>
-  <si>
-    <t>266e892a9e7102b2541374a4a283b9f6e012af49</t>
-  </si>
-  <si>
-    <t>46c825cb6f1efe399d339144749ed5f0c95b0314</t>
-  </si>
-  <si>
-    <t>149cab1dac170df649be1c0d08e446b58bb42a11</t>
-  </si>
-  <si>
-    <t>c2789f628c2c053b50986d25de057cb2efcc6953</t>
-  </si>
-  <si>
-    <t>24261cf767fea0e71d813e590e12d3debb7b97db</t>
-  </si>
-  <si>
     <t>d676dcc525a6c6a3e9007fd2cc6ea998c9d59da1</t>
   </si>
   <si>
@@ -566,6 +599,153 @@
     <t>427cc63764d547350d15e00e0ecbd65430fb4a4a</t>
   </si>
   <si>
+    <t>9039af46d4e38a8a8e10636383918cc7599f14ac</t>
+  </si>
+  <si>
+    <t>6a746a4d89d74b5dbbe3f19cc32dcda18b973cdd</t>
+  </si>
+  <si>
+    <t>fa526a98c0cd9a10e25418134ed8f1feee789972</t>
+  </si>
+  <si>
+    <t>f623a5786214b017dd8c3be28e5edce9341e370d</t>
+  </si>
+  <si>
+    <t>8b7f329183e21b365222401c8a2c7d32108f0ee5</t>
+  </si>
+  <si>
+    <t>b4288bc39397f9de68d3f3ada18bc7fe5435ab5e</t>
+  </si>
+  <si>
+    <t>3524bfd3b3e1d43d48860e330bf7f098f5763ea4</t>
+  </si>
+  <si>
+    <t>1f9af15e7163c754c1a17386e15654ca7cde0d5f</t>
+  </si>
+  <si>
+    <t>7b64b7fc69ad38c4cd9bd0616e68059d0661579f</t>
+  </si>
+  <si>
+    <t>ed901bc97fa12c1af56f660ebdba6d64d48ea7f5</t>
+  </si>
+  <si>
+    <t>767a26dd705df1bedc9aaf9001d14902d8e3791c</t>
+  </si>
+  <si>
+    <t>e01d03eefb3fbe5d50fb67c44384bb7f6c88162c</t>
+  </si>
+  <si>
+    <t>50536f1af0b45343984a6c8b746231ef514c61b3</t>
+  </si>
+  <si>
+    <t>31ab86dbeb55258eecc9107ce680a9a167f9a4d0</t>
+  </si>
+  <si>
+    <t>9faee918f98f785520625bc2035c2f660a1341da</t>
+  </si>
+  <si>
+    <t>92de5b1f09b7c7f11aaaecc9ac883dd24cf55232</t>
+  </si>
+  <si>
+    <t>caa7198e8a0d384df1c24c3e2d616e086d4eadfa</t>
+  </si>
+  <si>
+    <t>067130ecde7211d2063ba0e2a83e03daf7ab9e5e</t>
+  </si>
+  <si>
+    <t>bbb1bec1b9ccc1c34455e372d4729ec01c21c558</t>
+  </si>
+  <si>
+    <t>b8d26f83f26d4a5852d553b7733547b5aab81c84</t>
+  </si>
+  <si>
+    <t>df4cc6667dd1ad8fd49483f89f74f8129ce81453</t>
+  </si>
+  <si>
+    <t>9da052a45a8010ab38fc3c4722f98f75b72c72a2</t>
+  </si>
+  <si>
+    <t>e46163cba7bec7e43e12ae1e0f2dafad30e9fb8d</t>
+  </si>
+  <si>
+    <t>0552f8601850fd6e241d4be8c6a554b52f259cfa</t>
+  </si>
+  <si>
+    <t>5b34e0bd512e34b8578419d764efe5a8d430f474</t>
+  </si>
+  <si>
+    <t>4d4df7bd0c56b98dfab5bee5d0af8db807c0bdac</t>
+  </si>
+  <si>
+    <t>b48842091c0eab3974b4b65bf8174a9130fa6777</t>
+  </si>
+  <si>
+    <t>a5c76f6e0de129ae356187c87ba49502c74b56b6</t>
+  </si>
+  <si>
+    <t>3d3b2cd6d540543d36152e962bc23168fb00ce36</t>
+  </si>
+  <si>
+    <t>3affec34d8eeb4b8402369937c044abd0194cadc</t>
+  </si>
+  <si>
+    <t>c239d9cc56d49292d6d282cba6699f10ffbd196d</t>
+  </si>
+  <si>
+    <t>053fe9c7a842e861a73aa5531c71607202e60946</t>
+  </si>
+  <si>
+    <t>0dcac3044a2e691a59dadb2e0075b20e75ba4b1b</t>
+  </si>
+  <si>
+    <t>0dc22b129abe2d61b4fa736d306b75e90078cbc9</t>
+  </si>
+  <si>
+    <t>c616066a6048d01cd75bde374e863c3884016dcf</t>
+  </si>
+  <si>
+    <t>2299a326b51c966513461ac7a4536392c9443888</t>
+  </si>
+  <si>
+    <t>8fd0f7292594d7582bc97382808c717676812968</t>
+  </si>
+  <si>
+    <t>8024d0af3feb522eabeaad4773fa9a8b0d98f775</t>
+  </si>
+  <si>
+    <t>51741194de2aa9e257ccfd1451f3272842ce9403</t>
+  </si>
+  <si>
+    <t>74492d65f03c8749fc13cfbdf610e352ad2230ed</t>
+  </si>
+  <si>
+    <t>8829abe7402363ccdce6cea213f55bfad55515cb</t>
+  </si>
+  <si>
+    <t>ac3e6776bd1f37b0a4f2abd2a7ee0236a95a28ac</t>
+  </si>
+  <si>
+    <t>a677e98de0ca16b7884fd8ecf04a0d0af77cd923</t>
+  </si>
+  <si>
+    <t>eaa22e7a565170adea96f095b25dd1e9abeb25c5</t>
+  </si>
+  <si>
+    <t>f9b315a468cd4184e908757a49c763aa0d028af4</t>
+  </si>
+  <si>
+    <t>76e1d0e6f789f23877915477ca4f073e28105b33</t>
+  </si>
+  <si>
+    <t>9f676fecfaeda932504dad80480287c035494591</t>
+  </si>
+  <si>
+    <t>cca420d68d7026f9806c32db6125c167abaccecc</t>
+  </si>
+  <si>
+    <t>319646a8a14fc4d0c460164ef3c1a87ff870ae82</t>
+  </si>
+  <si>
     <t>8e4ba25e84038294546c4af12364a4d737e658a1</t>
   </si>
   <si>
@@ -575,42 +755,6 @@
     <t>e6770399e6643b5818c949c53d4bcc84fe799c8b</t>
   </si>
   <si>
-    <t>bbb1bec1b9ccc1c34455e372d4729ec01c21c558</t>
-  </si>
-  <si>
-    <t>b8d26f83f26d4a5852d553b7733547b5aab81c84</t>
-  </si>
-  <si>
-    <t>df4cc6667dd1ad8fd49483f89f74f8129ce81453</t>
-  </si>
-  <si>
-    <t>50536f1af0b45343984a6c8b746231ef514c61b3</t>
-  </si>
-  <si>
-    <t>31ab86dbeb55258eecc9107ce680a9a167f9a4d0</t>
-  </si>
-  <si>
-    <t>9faee918f98f785520625bc2035c2f660a1341da</t>
-  </si>
-  <si>
-    <t>9da052a45a8010ab38fc3c4722f98f75b72c72a2</t>
-  </si>
-  <si>
-    <t>e46163cba7bec7e43e12ae1e0f2dafad30e9fb8d</t>
-  </si>
-  <si>
-    <t>0552f8601850fd6e241d4be8c6a554b52f259cfa</t>
-  </si>
-  <si>
-    <t>9039af46d4e38a8a8e10636383918cc7599f14ac</t>
-  </si>
-  <si>
-    <t>6a746a4d89d74b5dbbe3f19cc32dcda18b973cdd</t>
-  </si>
-  <si>
-    <t>fa526a98c0cd9a10e25418134ed8f1feee789972</t>
-  </si>
-  <si>
     <t>b1afcef86f25397543f9a4c5d2b9f4fc38013526</t>
   </si>
   <si>
@@ -620,6 +764,81 @@
     <t>7cd9638ff60dd5f7d130413e7a8c20a7ddc8b48f</t>
   </si>
   <si>
+    <t>8c408cea23860abb5e80b49a051e0ae73eae5aad</t>
+  </si>
+  <si>
+    <t>c73d7fe32b150183866ecd2a448c04a4129328ad</t>
+  </si>
+  <si>
+    <t>5011cc4b310445198ba1406953265de323ba695e</t>
+  </si>
+  <si>
+    <t>5d5f0257f902dca2a920e87b9204b3ff4d5dd554</t>
+  </si>
+  <si>
+    <t>90ce6a5e79251f5173aa332eabafa413bec1b519</t>
+  </si>
+  <si>
+    <t>73b68a10db8226a753aa472158a0ce26736179e4</t>
+  </si>
+  <si>
+    <t>75fcdb2d4a35a21377f8c7319340768403cf1eea</t>
+  </si>
+  <si>
+    <t>0c7fd9e1dbbc8534bb07f41ac417f87e0b94f245</t>
+  </si>
+  <si>
+    <t>05a9083d0015b474f6ae1d6281f4d0ea9f8f34ab</t>
+  </si>
+  <si>
+    <t>e8e1f14c7c9c8dc7d615c4c95b3959305e05f9a9</t>
+  </si>
+  <si>
+    <t>d08cc2f5338752cf544c7fbc359c13aec0dd564c</t>
+  </si>
+  <si>
+    <t>1b925cf221b9fbcc5f63965b5b2931a9df5d003f</t>
+  </si>
+  <si>
+    <t>7fbdf24bcaa2a14f4d08f279c6f33ec2936c2d95</t>
+  </si>
+  <si>
+    <t>4695904fb518253262800dd16c8fec739cc7f7cb</t>
+  </si>
+  <si>
+    <t>d95e91d42475ada8977824dd4b219e2c00868665</t>
+  </si>
+  <si>
+    <t>4d02e29cbf2950a1027214833d288a947c3b5481</t>
+  </si>
+  <si>
+    <t>6700267ae9374cd4d589f1de4a5b086fb0bcbc19</t>
+  </si>
+  <si>
+    <t>3e55b44904264416c3217aa35ceaf252b71b4641</t>
+  </si>
+  <si>
+    <t>5e6e59b52866d5502c0b237f756184f6d7cef77d</t>
+  </si>
+  <si>
+    <t>46a0d4f6af2e0f33c9b2da1a4243353b0e5b7f14</t>
+  </si>
+  <si>
+    <t>a269950d7d44ec9895dd17d7663fc549cb56d8b0</t>
+  </si>
+  <si>
+    <t>9ad95223d1787e39818140d7562fb89165236ed3</t>
+  </si>
+  <si>
+    <t>f3a8d6f06cd478230efa9cc3477e31ae876d1cb5</t>
+  </si>
+  <si>
+    <t>e4386dd5378387afacf8289735e68763a2ed374c</t>
+  </si>
+  <si>
+    <t>abe2f8580b3340e2064cca81696c02931b641c84</t>
+  </si>
+  <si>
     <t>e163bdf634f7268095bf7eed93d2109a4bc03450</t>
   </si>
   <si>
@@ -629,184 +848,40 @@
     <t>47fa66a41206c5397d67ddddd53b7aa744391cbe</t>
   </si>
   <si>
-    <t>a5c76f6e0de129ae356187c87ba49502c74b56b6</t>
-  </si>
-  <si>
-    <t>3d3b2cd6d540543d36152e962bc23168fb00ce36</t>
-  </si>
-  <si>
-    <t>3affec34d8eeb4b8402369937c044abd0194cadc</t>
-  </si>
-  <si>
-    <t>ed901bc97fa12c1af56f660ebdba6d64d48ea7f5</t>
-  </si>
-  <si>
-    <t>767a26dd705df1bedc9aaf9001d14902d8e3791c</t>
-  </si>
-  <si>
-    <t>e01d03eefb3fbe5d50fb67c44384bb7f6c88162c</t>
-  </si>
-  <si>
-    <t>46a0d4f6af2e0f33c9b2da1a4243353b0e5b7f14</t>
-  </si>
-  <si>
-    <t>a269950d7d44ec9895dd17d7663fc549cb56d8b0</t>
-  </si>
-  <si>
-    <t>9ad95223d1787e39818140d7562fb89165236ed3</t>
-  </si>
-  <si>
-    <t>735ec9e3ac354172cc406eb782336bdcf677ce98</t>
-  </si>
-  <si>
-    <t>d33afd7a9a843a353eb29f5c59a1a6ecae91172e</t>
-  </si>
-  <si>
-    <t>4b09bff64b3aad5ddd945df8b6dc3c1cf1fd9010</t>
-  </si>
-  <si>
-    <t>5b34e0bd512e34b8578419d764efe5a8d430f474</t>
-  </si>
-  <si>
-    <t>4d4df7bd0c56b98dfab5bee5d0af8db807c0bdac</t>
-  </si>
-  <si>
-    <t>b48842091c0eab3974b4b65bf8174a9130fa6777</t>
-  </si>
-  <si>
-    <t>3524bfd3b3e1d43d48860e330bf7f098f5763ea4</t>
-  </si>
-  <si>
-    <t>1f9af15e7163c754c1a17386e15654ca7cde0d5f</t>
-  </si>
-  <si>
-    <t>7b64b7fc69ad38c4cd9bd0616e68059d0661579f</t>
-  </si>
-  <si>
-    <t>8024d0af3feb522eabeaad4773fa9a8b0d98f775</t>
-  </si>
-  <si>
-    <t>51741194de2aa9e257ccfd1451f3272842ce9403</t>
-  </si>
-  <si>
-    <t>74492d65f03c8749fc13cfbdf610e352ad2230ed</t>
-  </si>
-  <si>
-    <t>8829abe7402363ccdce6cea213f55bfad55515cb</t>
-  </si>
-  <si>
-    <t>ac3e6776bd1f37b0a4f2abd2a7ee0236a95a28ac</t>
-  </si>
-  <si>
-    <t>a677e98de0ca16b7884fd8ecf04a0d0af77cd923</t>
-  </si>
-  <si>
-    <t>9f676fecfaeda932504dad80480287c035494591</t>
-  </si>
-  <si>
-    <t>cca420d68d7026f9806c32db6125c167abaccecc</t>
-  </si>
-  <si>
-    <t>319646a8a14fc4d0c460164ef3c1a87ff870ae82</t>
-  </si>
-  <si>
-    <t>4695904fb518253262800dd16c8fec739cc7f7cb</t>
-  </si>
-  <si>
-    <t>d95e91d42475ada8977824dd4b219e2c00868665</t>
-  </si>
-  <si>
-    <t>4d02e29cbf2950a1027214833d288a947c3b5481</t>
-  </si>
-  <si>
-    <t>5d5f0257f902dca2a920e87b9204b3ff4d5dd554</t>
-  </si>
-  <si>
-    <t>90ce6a5e79251f5173aa332eabafa413bec1b519</t>
-  </si>
-  <si>
-    <t>73b68a10db8226a753aa472158a0ce26736179e4</t>
-  </si>
-  <si>
-    <t>6700267ae9374cd4d589f1de4a5b086fb0bcbc19</t>
-  </si>
-  <si>
-    <t>3e55b44904264416c3217aa35ceaf252b71b4641</t>
-  </si>
-  <si>
-    <t>5e6e59b52866d5502c0b237f756184f6d7cef77d</t>
-  </si>
-  <si>
-    <t>c239d9cc56d49292d6d282cba6699f10ffbd196d</t>
-  </si>
-  <si>
-    <t>053fe9c7a842e861a73aa5531c71607202e60946</t>
-  </si>
-  <si>
-    <t>f623a5786214b017dd8c3be28e5edce9341e370d</t>
-  </si>
-  <si>
-    <t>8b7f329183e21b365222401c8a2c7d32108f0ee5</t>
-  </si>
-  <si>
-    <t>b4288bc39397f9de68d3f3ada18bc7fe5435ab5e</t>
-  </si>
-  <si>
-    <t>2299a326b51c966513461ac7a4536392c9443888</t>
-  </si>
-  <si>
-    <t>8fd0f7292594d7582bc97382808c717676812968</t>
-  </si>
-  <si>
-    <t>d08cc2f5338752cf544c7fbc359c13aec0dd564c</t>
-  </si>
-  <si>
-    <t>1b925cf221b9fbcc5f63965b5b2931a9df5d003f</t>
-  </si>
-  <si>
-    <t>7fbdf24bcaa2a14f4d08f279c6f33ec2936c2d95</t>
-  </si>
-  <si>
-    <t>eaa22e7a565170adea96f095b25dd1e9abeb25c5</t>
-  </si>
-  <si>
-    <t>f9b315a468cd4184e908757a49c763aa0d028af4</t>
-  </si>
-  <si>
-    <t>76e1d0e6f789f23877915477ca4f073e28105b33</t>
-  </si>
-  <si>
-    <t>05a9083d0015b474f6ae1d6281f4d0ea9f8f34ab</t>
-  </si>
-  <si>
-    <t>e8e1f14c7c9c8dc7d615c4c95b3959305e05f9a9</t>
-  </si>
-  <si>
-    <t>92de5b1f09b7c7f11aaaecc9ac883dd24cf55232</t>
-  </si>
-  <si>
-    <t>caa7198e8a0d384df1c24c3e2d616e086d4eadfa</t>
-  </si>
-  <si>
-    <t>067130ecde7211d2063ba0e2a83e03daf7ab9e5e</t>
-  </si>
-  <si>
-    <t>f3a8d6f06cd478230efa9cc3477e31ae876d1cb5</t>
-  </si>
-  <si>
-    <t>e4386dd5378387afacf8289735e68763a2ed374c</t>
-  </si>
-  <si>
-    <t>abe2f8580b3340e2064cca81696c02931b641c84</t>
-  </si>
-  <si>
-    <t>5011cc4b310445198ba1406953265de323ba695e</t>
-  </si>
-  <si>
-    <t>75fcdb2d4a35a21377f8c7319340768403cf1eea</t>
-  </si>
-  <si>
-    <t>0c7fd9e1dbbc8534bb07f41ac417f87e0b94f245</t>
+    <t>c05f9fe98e999b5d378d9bd5e582a076dd0c2c12</t>
+  </si>
+  <si>
+    <t>41eec7806d81c64605e6f1b84454df31801a2488</t>
+  </si>
+  <si>
+    <t>c6c20234404536803f1e9d7fe0095e50db4c54a1</t>
+  </si>
+  <si>
+    <t>257acba31e9dccd78cede72e4a5b088549ef15e6</t>
+  </si>
+  <si>
+    <t>14cc447ae47e9df4370e8d81ccbeb81cf3bf672f</t>
+  </si>
+  <si>
+    <t>d87d51b7013134ead568ea3ef9119adaea0384a2</t>
+  </si>
+  <si>
+    <t>caf49aae352ac6e131b07d4a96d9cd1a4aa63d28</t>
+  </si>
+  <si>
+    <t>3278d38cbe61af7b4d0fca78a2cbd08c25a168af</t>
+  </si>
+  <si>
+    <t>f6a6a1ff88c4b81cdfbf71652b51ef76d0efc888</t>
+  </si>
+  <si>
+    <t>9334edc9eaf12db0280e0f1b3f95be621ab3752b</t>
+  </si>
+  <si>
+    <t>61549f13c04fdbb95b7a91742ba5a0000896fb5f</t>
+  </si>
+  <si>
+    <t>7849666529b4b5836808a912b87dc2fe55456980</t>
   </si>
   <si>
     <t>d100093be13dca2c370a39a8b90cb7a0145c516c</t>
@@ -818,19 +893,76 @@
     <t>63e31606e05d201d6e4a218ebf9fe8818e713863</t>
   </si>
   <si>
-    <t>8c408cea23860abb5e80b49a051e0ae73eae5aad</t>
-  </si>
-  <si>
-    <t>c73d7fe32b150183866ecd2a448c04a4129328ad</t>
-  </si>
-  <si>
-    <t>0dcac3044a2e691a59dadb2e0075b20e75ba4b1b</t>
-  </si>
-  <si>
-    <t>0dc22b129abe2d61b4fa736d306b75e90078cbc9</t>
-  </si>
-  <si>
-    <t>c616066a6048d01cd75bde374e863c3884016dcf</t>
+    <t>d745a1832dfc448439567a956510cab82a16045c</t>
+  </si>
+  <si>
+    <t>88cc4c987b26c2e9ebb37da4c944932f3ab729b6</t>
+  </si>
+  <si>
+    <t>1c1abae5bbf8357fb32044e766cb92b06603dcfe</t>
+  </si>
+  <si>
+    <t>e2197551ecfe72221d7157c8537dc545e51bade9</t>
+  </si>
+  <si>
+    <t>c21ee3ebf63a7c86b1042db48b11a8f5c6563634</t>
+  </si>
+  <si>
+    <t>e850fbf675336c9ad46b84ea2d0dc5c5988f9561</t>
+  </si>
+  <si>
+    <t>4e8e491035180f3c86e4a9f0f6233d6bd43dbe08</t>
+  </si>
+  <si>
+    <t>98e62211c604383a73cb3ec291ec0f9a78a77a3e</t>
+  </si>
+  <si>
+    <t>a6e5b2880b0548f35f300e47f558da57f440fc74</t>
+  </si>
+  <si>
+    <t>ce1940e4f36fe9a0bfc9dcc7911c4f695d4ae7af</t>
+  </si>
+  <si>
+    <t>d349557166142cd3a4ca3c54bfa2644c3efa8d45</t>
+  </si>
+  <si>
+    <t>41afea681850137303bf6088a740222f94ca717e</t>
+  </si>
+  <si>
+    <t>ae7323cbe02284bad8c0646cd052789b30386232</t>
+  </si>
+  <si>
+    <t>82b8a9335fd2b71280e581e6b7a9cf263a8b7394</t>
+  </si>
+  <si>
+    <t>6e67120b8e4362616e171ad293a43ce195f3f7cb</t>
+  </si>
+  <si>
+    <t>ad3ec657a7ce05e3ef4aa7ba5600263e9e9e41aa</t>
+  </si>
+  <si>
+    <t>a6338b8635d9506e67fa4ab446a7e35b4ed21e72</t>
+  </si>
+  <si>
+    <t>19c4a5c9616f8598db2abb9552cce6e738bbee1a</t>
+  </si>
+  <si>
+    <t>2876c7ce1626d93ace59aa4c539f5a2154bf7e08</t>
+  </si>
+  <si>
+    <t>241957507c57c6a3300093c1419c9689d458f086</t>
+  </si>
+  <si>
+    <t>3ea63b5bfb67ca4d2bd0c6e754d24a9e25daaeca</t>
+  </si>
+  <si>
+    <t>cdfce46a9fb6aedc70de5d769bbe18cc02bb73f0</t>
+  </si>
+  <si>
+    <t>0e9ed0c2e486583cb88a376749e0ab3f2413a2ec</t>
+  </si>
+  <si>
+    <t>7de546385a2c09c59eb6e23d7cffb37fe4c0b1b9</t>
   </si>
   <si>
     <t>20775791d9ce000b798255d57c5db4818fde57ac</t>
@@ -842,58 +974,172 @@
     <t>0977e1b487a82c5bf8fce8e8ac2d213a57b311f0</t>
   </si>
   <si>
-    <t>9334edc9eaf12db0280e0f1b3f95be621ab3752b</t>
-  </si>
-  <si>
-    <t>61549f13c04fdbb95b7a91742ba5a0000896fb5f</t>
-  </si>
-  <si>
-    <t>7849666529b4b5836808a912b87dc2fe55456980</t>
-  </si>
-  <si>
-    <t>c05f9fe98e999b5d378d9bd5e582a076dd0c2c12</t>
-  </si>
-  <si>
-    <t>41eec7806d81c64605e6f1b84454df31801a2488</t>
-  </si>
-  <si>
-    <t>c6c20234404536803f1e9d7fe0095e50db4c54a1</t>
-  </si>
-  <si>
-    <t>257acba31e9dccd78cede72e4a5b088549ef15e6</t>
-  </si>
-  <si>
-    <t>14cc447ae47e9df4370e8d81ccbeb81cf3bf672f</t>
-  </si>
-  <si>
-    <t>d87d51b7013134ead568ea3ef9119adaea0384a2</t>
-  </si>
-  <si>
-    <t>caf49aae352ac6e131b07d4a96d9cd1a4aa63d28</t>
-  </si>
-  <si>
-    <t>3278d38cbe61af7b4d0fca78a2cbd08c25a168af</t>
-  </si>
-  <si>
-    <t>f6a6a1ff88c4b81cdfbf71652b51ef76d0efc888</t>
-  </si>
-  <si>
-    <t>d745a1832dfc448439567a956510cab82a16045c</t>
-  </si>
-  <si>
-    <t>88cc4c987b26c2e9ebb37da4c944932f3ab729b6</t>
-  </si>
-  <si>
-    <t>1c1abae5bbf8357fb32044e766cb92b06603dcfe</t>
-  </si>
-  <si>
-    <t>ce1940e4f36fe9a0bfc9dcc7911c4f695d4ae7af</t>
-  </si>
-  <si>
-    <t>d349557166142cd3a4ca3c54bfa2644c3efa8d45</t>
-  </si>
-  <si>
-    <t>41afea681850137303bf6088a740222f94ca717e</t>
+    <t>f00b3005c7b8dece222187bc224f4e2cc58eb343</t>
+  </si>
+  <si>
+    <t>d6ecc032c2ec342522622afe358383eee81f2230</t>
+  </si>
+  <si>
+    <t>39ec137047d92d3b4de889b384ea64eedc950e60</t>
+  </si>
+  <si>
+    <t>5b1287ad413ca3a9ceeb181bcd387eba0a91aab8</t>
+  </si>
+  <si>
+    <t>8428cc5b9922080661626d241d1e745117ff9491</t>
+  </si>
+  <si>
+    <t>97e8c35f70afed96a380531bdea815ba83683ef6</t>
+  </si>
+  <si>
+    <t>7efa6fe57d9e41869ed177aeb1bd6789c1ed64c3</t>
+  </si>
+  <si>
+    <t>13be8f3a051c1aa8b6f3158bdaf7fec5b6837277</t>
+  </si>
+  <si>
+    <t>9d26381dcc36545138504b64f39d40956c9dd821</t>
+  </si>
+  <si>
+    <t>458235e444776694403ed8032af3c8bacb66001d</t>
+  </si>
+  <si>
+    <t>a30c1c28089336f6e12be826c7f9c0200752172a</t>
+  </si>
+  <si>
+    <t>664abe70626acf5a0e23439f6e900c1803427784</t>
+  </si>
+  <si>
+    <t>5f6bcc4a351d9079a8223e8b53c235532f750995</t>
+  </si>
+  <si>
+    <t>7288e6c980ea2ea310d0790f3f686ef6f22d1076</t>
+  </si>
+  <si>
+    <t>8242735d84407c672410291a9151e6c1f5efc2f1</t>
+  </si>
+  <si>
+    <t>dc267ea5681e73aa6eac55d34da370c3735f0839</t>
+  </si>
+  <si>
+    <t>8775472af7156b7abef2b9d0ffad1939e5a2ad49</t>
+  </si>
+  <si>
+    <t>2f38261de837b55c86b34053768bed05139e1743</t>
+  </si>
+  <si>
+    <t>2dd66847cfe5affca733de4a281e9eaba395b343</t>
+  </si>
+  <si>
+    <t>7ba3b123131bdd792bbca9e46e7a7497895e101e</t>
+  </si>
+  <si>
+    <t>22ff197f02fde92c7cceead31a1f06809282f2d9</t>
+  </si>
+  <si>
+    <t>5d3bb791fd9293f761c53e600e333b5b1c3203ed</t>
+  </si>
+  <si>
+    <t>8d138cd1e9f8786211025ade02f6666860eef724</t>
+  </si>
+  <si>
+    <t>a0020f033980ab047e0fb37004d03327dcebbbf9</t>
+  </si>
+  <si>
+    <t>c660833697e4b3b92f6c4a51bfc90b7bcb88074b</t>
+  </si>
+  <si>
+    <t>a131434f94acdf5b81d73d0005757ace9422ff17</t>
+  </si>
+  <si>
+    <t>41ee23716190648bbaf08f837f1710617fe19bbc</t>
+  </si>
+  <si>
+    <t>f46d47a966195b53933c9d771a362ef5e2ef4328</t>
+  </si>
+  <si>
+    <t>512d68f79317290ba565b0a15080201823c7f73c</t>
+  </si>
+  <si>
+    <t>e782077e23659d2fc44c519ba765079846c132e1</t>
+  </si>
+  <si>
+    <t>cd13d267111febda4c1510da5521a16a22324ace</t>
+  </si>
+  <si>
+    <t>9e84834620b32343a169da1a454d7380ede38886</t>
+  </si>
+  <si>
+    <t>51917c7413ccf5e47594c62829fbd5940180cbb7</t>
+  </si>
+  <si>
+    <t>f85ca1f88ff62b8e12ef355de9e7d87df01b13df</t>
+  </si>
+  <si>
+    <t>423f6cc9da8cc5ecac95f3e763cd61636b0df45b</t>
+  </si>
+  <si>
+    <t>1c139ca6bca08d33a7f0963a27b568b32a96d4ce</t>
+  </si>
+  <si>
+    <t>916384248ab9fd667b5ad830235d28d2d889b648</t>
+  </si>
+  <si>
+    <t>28d74d07ac9861a0ac1c688b536652e915bcb155</t>
+  </si>
+  <si>
+    <t>3e3407eb993c7ec9147bafe400dfb60102691169</t>
+  </si>
+  <si>
+    <t>ff0c1cfd7f857e6aaec8b45b96c48bb9cc5fa0b9</t>
+  </si>
+  <si>
+    <t>2b39b434fac1fa7d4a0e382e8ab9fe5552499eef</t>
+  </si>
+  <si>
+    <t>4d176c84948e9d92288dfcb0be6c721eee130d66</t>
+  </si>
+  <si>
+    <t>1ae06b89e4cc639a638e8745a36535c3c3bc3468</t>
+  </si>
+  <si>
+    <t>5b97d565cd6632ed340f6d8ae077e31cbd253e83</t>
+  </si>
+  <si>
+    <t>fd0e0de164310dd463d11253ade9e01dc55f851d</t>
+  </si>
+  <si>
+    <t>2fefcf8834ede9c73fbd64a16d04fe2ffd25a425</t>
+  </si>
+  <si>
+    <t>2a01f6b9fca6826331e3cea2de549d8514667896</t>
+  </si>
+  <si>
+    <t>5fabb0b757190ac62309cd11eb5531fea30f0176</t>
+  </si>
+  <si>
+    <t>a331ed546dcf90a0b9d966bc694e40c5780ba708</t>
+  </si>
+  <si>
+    <t>f1292fb7fe3cfc41430ddd5ddd8f2af0a993ae0d</t>
+  </si>
+  <si>
+    <t>a210210b202c85cdfacf499c4376e99c4507a987</t>
+  </si>
+  <si>
+    <t>d608974c17f8f2f3d5f6ad936fda5c9c119cbb84</t>
+  </si>
+  <si>
+    <t>e052ddab2fb607c0269d566f005524a51bcddbe1</t>
+  </si>
+  <si>
+    <t>e591c1869a4c6e59d45850fcebaa76fdf0b67b0f</t>
+  </si>
+  <si>
+    <t>dee820b8fd7cd0cfb364cb4aca68bded0c33ab5f</t>
+  </si>
+  <si>
+    <t>aff79197807f0ddcd16dc438d82751fb47c59e3f</t>
   </si>
   <si>
     <t>d3a4c3c7188836b8a6abf8761f73341c4421bb93</t>
@@ -905,49 +1151,13 @@
     <t>83d86bcf9bba3e39337650fa6bae68c17effaf59</t>
   </si>
   <si>
-    <t>c660833697e4b3b92f6c4a51bfc90b7bcb88074b</t>
-  </si>
-  <si>
-    <t>a131434f94acdf5b81d73d0005757ace9422ff17</t>
-  </si>
-  <si>
-    <t>41ee23716190648bbaf08f837f1710617fe19bbc</t>
-  </si>
-  <si>
-    <t>2876c7ce1626d93ace59aa4c539f5a2154bf7e08</t>
-  </si>
-  <si>
-    <t>241957507c57c6a3300093c1419c9689d458f086</t>
-  </si>
-  <si>
-    <t>3ea63b5bfb67ca4d2bd0c6e754d24a9e25daaeca</t>
-  </si>
-  <si>
-    <t>a210210b202c85cdfacf499c4376e99c4507a987</t>
-  </si>
-  <si>
-    <t>d608974c17f8f2f3d5f6ad936fda5c9c119cbb84</t>
-  </si>
-  <si>
-    <t>e052ddab2fb607c0269d566f005524a51bcddbe1</t>
-  </si>
-  <si>
-    <t>e2197551ecfe72221d7157c8537dc545e51bade9</t>
-  </si>
-  <si>
-    <t>c21ee3ebf63a7c86b1042db48b11a8f5c6563634</t>
-  </si>
-  <si>
-    <t>e850fbf675336c9ad46b84ea2d0dc5c5988f9561</t>
-  </si>
-  <si>
-    <t>f00b3005c7b8dece222187bc224f4e2cc58eb343</t>
-  </si>
-  <si>
-    <t>d6ecc032c2ec342522622afe358383eee81f2230</t>
-  </si>
-  <si>
-    <t>39ec137047d92d3b4de889b384ea64eedc950e60</t>
+    <t>8cce737523806c3bf4a1aa65a716664c032460f9</t>
+  </si>
+  <si>
+    <t>126aa1b40acef366bc21bc2a99e1eab1fad932ba</t>
+  </si>
+  <si>
+    <t>efc5ea23bfcc6fb5ddc211e9a45f824ed751fc8f</t>
   </si>
 </sst>
 </file>
@@ -992,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1053,10 +1263,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.23499999940395355</v>
+        <v>0.6740000247955322</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1073,10 +1283,10 @@
         <v>1.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -1085,10 +1295,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.7400000095367432</v>
+        <v>0.3100000023841858</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1105,10 +1315,10 @@
         <v>1.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -1117,10 +1327,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.22599999606609344</v>
+        <v>0.40700000524520874</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1149,10 +1359,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>0.14300000667572021</v>
+        <v>0.06499999761581421</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1166,13 +1376,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>43.0</v>
+        <v>52.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -1181,10 +1391,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>20.23400115966797</v>
+        <v>19.046998977661133</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1198,13 +1408,13 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>43.0</v>
+        <v>52.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -1213,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>29.117998123168945</v>
+        <v>19.489002227783203</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1233,10 +1443,10 @@
         <v>57.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G8" t="b" s="0">
         <v>0</v>
@@ -1245,10 +1455,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>41.9379997253418</v>
+        <v>33.62099838256836</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1262,13 +1472,13 @@
         <v>33</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>48.0</v>
+        <v>57.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -1277,10 +1487,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>30.624000549316406</v>
+        <v>32.23099899291992</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1294,13 +1504,13 @@
         <v>36</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>48.0</v>
+        <v>54.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>4.0</v>
+        <v>27.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
       <c r="G10" t="b" s="0">
         <v>0</v>
@@ -1309,10 +1519,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>25.429000854492188</v>
+        <v>33.63100051879883</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1326,13 +1536,13 @@
         <v>39</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>52.0</v>
+        <v>177.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
@@ -1341,10 +1551,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>32.722999572753906</v>
+        <v>120.12699127197266</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1358,13 +1568,13 @@
         <v>42</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1.0</v>
+        <v>54.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="G12" t="b" s="0">
         <v>0</v>
@@ -1373,10 +1583,10 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>0.20999999344348907</v>
+        <v>59.11300277709961</v>
       </c>
       <c r="J12" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1390,13 +1600,13 @@
         <v>45</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>118.0</v>
+        <v>54.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G13" t="b" s="0">
         <v>0</v>
@@ -1405,10 +1615,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>83.15900421142578</v>
+        <v>70.5429916381836</v>
       </c>
       <c r="J13" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1422,7 +1632,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>45.0</v>
+        <v>54.0</v>
       </c>
       <c r="E14" t="n" s="0">
         <v>2.0</v>
@@ -1437,10 +1647,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>22.19300079345703</v>
+        <v>66.02099609375</v>
       </c>
       <c r="J14" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1454,13 +1664,13 @@
         <v>51</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>45.0</v>
+        <v>177.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" t="b" s="0">
         <v>0</v>
@@ -1469,10 +1679,10 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>31.2030029296875</v>
+        <v>205.15997314453125</v>
       </c>
       <c r="J15" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1486,13 +1696,13 @@
         <v>54</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>45.0</v>
+        <v>177.0</v>
       </c>
       <c r="E16" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F16" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" t="b" s="0">
         <v>0</v>
@@ -1501,30 +1711,30 @@
         <v>1</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>36.12199783325195</v>
+        <v>207.01202392578125</v>
       </c>
       <c r="J16" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B17" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="C17" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="C17" t="s" s="0">
-        <v>57</v>
-      </c>
       <c r="D17" t="n" s="0">
-        <v>45.0</v>
+        <v>177.0</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G17" t="b" s="0">
         <v>0</v>
@@ -1533,24 +1743,24 @@
         <v>1</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>28.13599967956543</v>
+        <v>186.61398315429688</v>
       </c>
       <c r="J17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="C18" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="C18" t="s" s="0">
-        <v>60</v>
-      </c>
       <c r="D18" t="n" s="0">
-        <v>123.0</v>
+        <v>177.0</v>
       </c>
       <c r="E18" t="n" s="0">
         <v>1.0</v>
@@ -1565,30 +1775,30 @@
         <v>1</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>94.36199951171875</v>
+        <v>217.66502380371094</v>
       </c>
       <c r="J18" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="B19" t="s" s="0">
+      <c r="C19" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="C19" t="s" s="0">
-        <v>63</v>
-      </c>
       <c r="D19" t="n" s="0">
-        <v>1.0</v>
+        <v>177.0</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G19" t="b" s="0">
         <v>0</v>
@@ -1597,24 +1807,24 @@
         <v>1</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>1.496999979019165</v>
+        <v>203.2890167236328</v>
       </c>
       <c r="J19" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B20" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="B20" t="s" s="0">
+      <c r="C20" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="C20" t="s" s="0">
-        <v>66</v>
-      </c>
       <c r="D20" t="n" s="0">
-        <v>123.0</v>
+        <v>52.0</v>
       </c>
       <c r="E20" t="n" s="0">
         <v>1.0</v>
@@ -1629,30 +1839,30 @@
         <v>1</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>100.66300964355469</v>
+        <v>40.165000915527344</v>
       </c>
       <c r="J20" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="B21" t="s" s="0">
+      <c r="C21" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="C21" t="s" s="0">
-        <v>69</v>
-      </c>
       <c r="D21" t="n" s="0">
-        <v>620.0</v>
+        <v>172.0</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G21" t="b" s="0">
         <v>0</v>
@@ -1661,30 +1871,30 @@
         <v>1</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>290.5350036621094</v>
+        <v>196.51400756835938</v>
       </c>
       <c r="J21" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="B22" t="s" s="0">
+      <c r="C22" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="C22" t="s" s="0">
-        <v>72</v>
-      </c>
       <c r="D22" t="n" s="0">
-        <v>620.0</v>
+        <v>1.0</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G22" t="b" s="0">
         <v>0</v>
@@ -1693,30 +1903,30 @@
         <v>1</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>284.5740051269531</v>
+        <v>0.42800000309944153</v>
       </c>
       <c r="J22" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="B23" t="s" s="0">
+      <c r="C23" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="C23" t="s" s="0">
-        <v>75</v>
-      </c>
       <c r="D23" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G23" t="b" s="0">
         <v>0</v>
@@ -1725,30 +1935,30 @@
         <v>1</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>0.3059999942779541</v>
+        <v>0.13099999725818634</v>
       </c>
       <c r="J23" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="B24" t="s" s="0">
+      <c r="C24" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="C24" t="s" s="0">
-        <v>45</v>
-      </c>
       <c r="D24" t="n" s="0">
-        <v>76.0</v>
+        <v>1.0</v>
       </c>
       <c r="E24" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F24" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G24" t="b" s="0">
         <v>0</v>
@@ -1757,10 +1967,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>77.21199798583984</v>
+        <v>0.4090000092983246</v>
       </c>
       <c r="J24" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1774,7 +1984,7 @@
         <v>80</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>45.0</v>
+        <v>625.0</v>
       </c>
       <c r="E25" t="n" s="0">
         <v>1.0</v>
@@ -1789,10 +1999,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>32.672000885009766</v>
+        <v>463.03607177734375</v>
       </c>
       <c r="J25" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1806,13 +2016,13 @@
         <v>83</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>172.0</v>
+        <v>54.0</v>
       </c>
       <c r="E26" t="n" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F26" t="n" s="0">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" t="b" s="0">
         <v>0</v>
@@ -1821,15 +2031,15 @@
         <v>1</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>149.37001037597656</v>
+        <v>77.48400115966797</v>
       </c>
       <c r="J26" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s" s="0">
         <v>84</v>
@@ -1838,7 +2048,7 @@
         <v>85</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>123.0</v>
+        <v>625.0</v>
       </c>
       <c r="E27" t="n" s="0">
         <v>1.0</v>
@@ -1853,10 +2063,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n" s="0">
-        <v>232.29498291015625</v>
+        <v>477.77001953125</v>
       </c>
       <c r="J27" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1870,13 +2080,13 @@
         <v>88</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>123.0</v>
+        <v>625.0</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>79.0</v>
+        <v>1.0</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>77.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" t="b" s="0">
         <v>0</v>
@@ -1885,10 +2095,10 @@
         <v>1</v>
       </c>
       <c r="I28" t="n" s="0">
-        <v>224.0369873046875</v>
+        <v>484.1589660644531</v>
       </c>
       <c r="J28" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1902,7 +2112,7 @@
         <v>91</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>123.0</v>
+        <v>625.0</v>
       </c>
       <c r="E29" t="n" s="0">
         <v>1.0</v>
@@ -1917,30 +2127,30 @@
         <v>1</v>
       </c>
       <c r="I29" t="n" s="0">
-        <v>215.51100158691406</v>
+        <v>446.18304443359375</v>
       </c>
       <c r="J29" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B30" t="s" s="0">
+      <c r="C30" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="C30" t="s" s="0">
-        <v>94</v>
-      </c>
       <c r="D30" t="n" s="0">
-        <v>118.0</v>
+        <v>625.0</v>
       </c>
       <c r="E30" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F30" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G30" t="b" s="0">
         <v>0</v>
@@ -1949,27 +2159,27 @@
         <v>1</v>
       </c>
       <c r="I30" t="n" s="0">
-        <v>262.7229919433594</v>
+        <v>489.48095703125</v>
       </c>
       <c r="J30" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B31" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="B31" t="s" s="0">
-        <v>96</v>
-      </c>
       <c r="C31" t="s" s="0">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>123.0</v>
+        <v>621.0</v>
       </c>
       <c r="E31" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F31" t="n" s="0">
         <v>1.0</v>
@@ -1981,24 +2191,24 @@
         <v>1</v>
       </c>
       <c r="I31" t="n" s="0">
-        <v>276.53900146484375</v>
+        <v>487.9320373535156</v>
       </c>
       <c r="J31" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>123.0</v>
+        <v>625.0</v>
       </c>
       <c r="E32" t="n" s="0">
         <v>1.0</v>
@@ -2013,24 +2223,24 @@
         <v>1</v>
       </c>
       <c r="I32" t="n" s="0">
-        <v>240.83700561523438</v>
+        <v>499.69488525390625</v>
       </c>
       <c r="J32" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>123.0</v>
+        <v>625.0</v>
       </c>
       <c r="E33" t="n" s="0">
         <v>1.0</v>
@@ -2045,30 +2255,30 @@
         <v>1</v>
       </c>
       <c r="I33" t="n" s="0">
-        <v>226.92201232910156</v>
+        <v>501.1280517578125</v>
       </c>
       <c r="J33" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B34" t="s" s="0">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s" s="0">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>123.0</v>
+        <v>621.0</v>
       </c>
       <c r="E34" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F34" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" t="b" s="0">
         <v>0</v>
@@ -2077,30 +2287,30 @@
         <v>1</v>
       </c>
       <c r="I34" t="n" s="0">
-        <v>218.24000549316406</v>
+        <v>480.7989807128906</v>
       </c>
       <c r="J34" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="B35" t="s" s="0">
+      <c r="C35" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="C35" t="s" s="0">
-        <v>106</v>
-      </c>
       <c r="D35" t="n" s="0">
-        <v>102.0</v>
+        <v>625.0</v>
       </c>
       <c r="E35" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F35" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" t="b" s="0">
         <v>0</v>
@@ -2109,30 +2319,30 @@
         <v>1</v>
       </c>
       <c r="I35" t="n" s="0">
-        <v>85.17500305175781</v>
+        <v>463.34197998046875</v>
       </c>
       <c r="J35" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="B36" t="s" s="0">
+      <c r="C36" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="C36" t="s" s="0">
-        <v>109</v>
-      </c>
       <c r="D36" t="n" s="0">
-        <v>110.0</v>
+        <v>625.0</v>
       </c>
       <c r="E36" t="n" s="0">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="F36" t="n" s="0">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="G36" t="b" s="0">
         <v>0</v>
@@ -2141,30 +2351,30 @@
         <v>1</v>
       </c>
       <c r="I36" t="n" s="0">
-        <v>129.22201538085938</v>
+        <v>461.89996337890625</v>
       </c>
       <c r="J36" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B37" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="B37" t="s" s="0">
+      <c r="C37" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="C37" t="s" s="0">
-        <v>112</v>
-      </c>
       <c r="D37" t="n" s="0">
-        <v>102.0</v>
+        <v>625.0</v>
       </c>
       <c r="E37" t="n" s="0">
-        <v>1.0</v>
+        <v>79.0</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>1.0</v>
+        <v>77.0</v>
       </c>
       <c r="G37" t="b" s="0">
         <v>0</v>
@@ -2173,24 +2383,24 @@
         <v>1</v>
       </c>
       <c r="I37" t="n" s="0">
-        <v>87.947998046875</v>
+        <v>501.72509765625</v>
       </c>
       <c r="J37" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B38" t="s" s="0">
         <v>113</v>
       </c>
-      <c r="B38" t="s" s="0">
+      <c r="C38" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="C38" t="s" s="0">
-        <v>115</v>
-      </c>
       <c r="D38" t="n" s="0">
-        <v>118.0</v>
+        <v>172.0</v>
       </c>
       <c r="E38" t="n" s="0">
         <v>29.0</v>
@@ -2205,30 +2415,30 @@
         <v>1</v>
       </c>
       <c r="I38" t="n" s="0">
-        <v>260.9309997558594</v>
+        <v>238.55899047851562</v>
       </c>
       <c r="J38" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B39" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="B39" t="s" s="0">
+      <c r="C39" t="s" s="0">
         <v>117</v>
       </c>
-      <c r="C39" t="s" s="0">
-        <v>118</v>
-      </c>
       <c r="D39" t="n" s="0">
-        <v>102.0</v>
+        <v>156.0</v>
       </c>
       <c r="E39" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F39" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G39" t="b" s="0">
         <v>0</v>
@@ -2237,27 +2447,27 @@
         <v>1</v>
       </c>
       <c r="I39" t="n" s="0">
-        <v>91.41699981689453</v>
+        <v>207.7230224609375</v>
       </c>
       <c r="J39" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="B40" t="s" s="0">
+      <c r="C40" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="C40" t="s" s="0">
-        <v>121</v>
-      </c>
       <c r="D40" t="n" s="0">
-        <v>102.0</v>
+        <v>156.0</v>
       </c>
       <c r="E40" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F40" t="n" s="0">
         <v>3.0</v>
@@ -2269,30 +2479,30 @@
         <v>1</v>
       </c>
       <c r="I40" t="n" s="0">
-        <v>225.93699645996094</v>
+        <v>180.69398498535156</v>
       </c>
       <c r="J40" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B41" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="B41" t="s" s="0">
+      <c r="C41" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="C41" t="s" s="0">
-        <v>124</v>
-      </c>
       <c r="D41" t="n" s="0">
-        <v>616.0</v>
+        <v>156.0</v>
       </c>
       <c r="E41" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F41" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G41" t="b" s="0">
         <v>0</v>
@@ -2301,30 +2511,30 @@
         <v>1</v>
       </c>
       <c r="I41" t="n" s="0">
-        <v>351.7929992675781</v>
+        <v>187.26300048828125</v>
       </c>
       <c r="J41" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B42" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="B42" t="s" s="0">
+      <c r="C42" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="C42" t="s" s="0">
-        <v>127</v>
-      </c>
       <c r="D42" t="n" s="0">
-        <v>102.0</v>
+        <v>613.0</v>
       </c>
       <c r="E42" t="n" s="0">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="F42" t="n" s="0">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="G42" t="b" s="0">
         <v>0</v>
@@ -2333,30 +2543,30 @@
         <v>1</v>
       </c>
       <c r="I42" t="n" s="0">
-        <v>223.3109893798828</v>
+        <v>406.3829650878906</v>
       </c>
       <c r="J42" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B43" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="B43" t="s" s="0">
+      <c r="C43" t="s" s="0">
         <v>129</v>
       </c>
-      <c r="C43" t="s" s="0">
-        <v>130</v>
-      </c>
       <c r="D43" t="n" s="0">
-        <v>102.0</v>
+        <v>621.0</v>
       </c>
       <c r="E43" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F43" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G43" t="b" s="0">
         <v>0</v>
@@ -2365,24 +2575,24 @@
         <v>1</v>
       </c>
       <c r="I43" t="n" s="0">
-        <v>217.56700134277344</v>
+        <v>406.3349609375</v>
       </c>
       <c r="J43" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B44" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="C44" t="s" s="0">
         <v>132</v>
       </c>
-      <c r="C44" t="s" s="0">
-        <v>133</v>
-      </c>
       <c r="D44" t="n" s="0">
-        <v>616.0</v>
+        <v>621.0</v>
       </c>
       <c r="E44" t="n" s="0">
         <v>3.0</v>
@@ -2397,30 +2607,30 @@
         <v>1</v>
       </c>
       <c r="I44" t="n" s="0">
-        <v>680.6561279296875</v>
+        <v>438.6010437011719</v>
       </c>
       <c r="J44" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B45" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="B45" t="s" s="0">
+      <c r="C45" t="s" s="0">
         <v>135</v>
       </c>
-      <c r="C45" t="s" s="0">
-        <v>136</v>
-      </c>
       <c r="D45" t="n" s="0">
-        <v>595.0</v>
+        <v>156.0</v>
       </c>
       <c r="E45" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F45" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G45" t="b" s="0">
         <v>0</v>
@@ -2429,30 +2639,30 @@
         <v>1</v>
       </c>
       <c r="I45" t="n" s="0">
-        <v>258.5369567871094</v>
+        <v>216.9320068359375</v>
       </c>
       <c r="J45" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B46" t="s" s="0">
         <v>137</v>
       </c>
-      <c r="B46" t="s" s="0">
+      <c r="C46" t="s" s="0">
         <v>138</v>
       </c>
-      <c r="C46" t="s" s="0">
-        <v>139</v>
-      </c>
       <c r="D46" t="n" s="0">
-        <v>102.0</v>
+        <v>621.0</v>
       </c>
       <c r="E46" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F46" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G46" t="b" s="0">
         <v>0</v>
@@ -2461,30 +2671,30 @@
         <v>1</v>
       </c>
       <c r="I46" t="n" s="0">
-        <v>201.22299194335938</v>
+        <v>416.5660400390625</v>
       </c>
       <c r="J46" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B47" t="s" s="0">
         <v>140</v>
       </c>
-      <c r="B47" t="s" s="0">
+      <c r="C47" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="C47" t="s" s="0">
-        <v>142</v>
-      </c>
       <c r="D47" t="n" s="0">
-        <v>102.0</v>
+        <v>606.0</v>
       </c>
       <c r="E47" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F47" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G47" t="b" s="0">
         <v>0</v>
@@ -2493,30 +2703,30 @@
         <v>1</v>
       </c>
       <c r="I47" t="n" s="0">
-        <v>184.02398681640625</v>
+        <v>407.95501708984375</v>
       </c>
       <c r="J47" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B48" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="B48" t="s" s="0">
+      <c r="C48" t="s" s="0">
         <v>144</v>
       </c>
-      <c r="C48" t="s" s="0">
-        <v>145</v>
-      </c>
       <c r="D48" t="n" s="0">
-        <v>102.0</v>
+        <v>606.0</v>
       </c>
       <c r="E48" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F48" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G48" t="b" s="0">
         <v>0</v>
@@ -2525,24 +2735,24 @@
         <v>1</v>
       </c>
       <c r="I48" t="n" s="0">
-        <v>205.6859893798828</v>
+        <v>381.0950012207031</v>
       </c>
       <c r="J48" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B49" t="s" s="0">
         <v>146</v>
       </c>
-      <c r="B49" t="s" s="0">
+      <c r="C49" t="s" s="0">
         <v>147</v>
       </c>
-      <c r="C49" t="s" s="0">
-        <v>148</v>
-      </c>
       <c r="D49" t="n" s="0">
-        <v>102.0</v>
+        <v>606.0</v>
       </c>
       <c r="E49" t="n" s="0">
         <v>1.0</v>
@@ -2557,24 +2767,24 @@
         <v>1</v>
       </c>
       <c r="I49" t="n" s="0">
-        <v>198.00599670410156</v>
+        <v>420.38800048828125</v>
       </c>
       <c r="J49" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="B50" t="s" s="0">
         <v>149</v>
       </c>
-      <c r="B50" t="s" s="0">
+      <c r="C50" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="C50" t="s" s="0">
-        <v>151</v>
-      </c>
       <c r="D50" t="n" s="0">
-        <v>592.0</v>
+        <v>606.0</v>
       </c>
       <c r="E50" t="n" s="0">
         <v>1.0</v>
@@ -2589,24 +2799,24 @@
         <v>1</v>
       </c>
       <c r="I50" t="n" s="0">
-        <v>587.6799926757812</v>
+        <v>406.821044921875</v>
       </c>
       <c r="J50" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B51" t="s" s="0">
         <v>152</v>
       </c>
-      <c r="B51" t="s" s="0">
+      <c r="C51" t="s" s="0">
         <v>153</v>
       </c>
-      <c r="C51" t="s" s="0">
-        <v>154</v>
-      </c>
       <c r="D51" t="n" s="0">
-        <v>102.0</v>
+        <v>606.0</v>
       </c>
       <c r="E51" t="n" s="0">
         <v>10.0</v>
@@ -2621,30 +2831,30 @@
         <v>1</v>
       </c>
       <c r="I51" t="n" s="0">
-        <v>213.33001708984375</v>
+        <v>417.31805419921875</v>
       </c>
       <c r="J51" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B52" t="s" s="0">
         <v>155</v>
       </c>
-      <c r="B52" t="s" s="0">
+      <c r="C52" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="C52" t="s" s="0">
-        <v>157</v>
-      </c>
       <c r="D52" t="n" s="0">
-        <v>616.0</v>
+        <v>606.0</v>
       </c>
       <c r="E52" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F52" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G52" t="b" s="0">
         <v>0</v>
@@ -2653,30 +2863,30 @@
         <v>1</v>
       </c>
       <c r="I52" t="n" s="0">
-        <v>763.1731567382812</v>
+        <v>417.0550537109375</v>
       </c>
       <c r="J52" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="C53" t="s" s="0">
         <v>158</v>
       </c>
-      <c r="B53" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="C53" t="s" s="0">
-        <v>160</v>
-      </c>
       <c r="D53" t="n" s="0">
-        <v>595.0</v>
+        <v>607.0</v>
       </c>
       <c r="E53" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F53" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G53" t="b" s="0">
         <v>0</v>
@@ -2685,30 +2895,30 @@
         <v>1</v>
       </c>
       <c r="I53" t="n" s="0">
-        <v>255.0049591064453</v>
+        <v>413.7100524902344</v>
       </c>
       <c r="J53" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="B54" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="C54" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="C54" t="s" s="0">
-        <v>162</v>
-      </c>
       <c r="D54" t="n" s="0">
-        <v>102.0</v>
+        <v>606.0</v>
       </c>
       <c r="E54" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F54" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G54" t="b" s="0">
         <v>0</v>
@@ -2717,30 +2927,30 @@
         <v>1</v>
       </c>
       <c r="I54" t="n" s="0">
-        <v>169.87098693847656</v>
+        <v>416.6650085449219</v>
       </c>
       <c r="J54" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B55" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="B55" t="s" s="0">
+      <c r="C55" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="C55" t="s" s="0">
-        <v>165</v>
-      </c>
       <c r="D55" t="n" s="0">
-        <v>595.0</v>
+        <v>615.0</v>
       </c>
       <c r="E55" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F55" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G55" t="b" s="0">
         <v>0</v>
@@ -2749,30 +2959,30 @@
         <v>1</v>
       </c>
       <c r="I55" t="n" s="0">
-        <v>619.6400146484375</v>
+        <v>455.0669860839844</v>
       </c>
       <c r="J55" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B56" t="s" s="0">
         <v>166</v>
       </c>
-      <c r="B56" t="s" s="0">
+      <c r="C56" t="s" s="0">
         <v>167</v>
       </c>
-      <c r="C56" t="s" s="0">
-        <v>168</v>
-      </c>
       <c r="D56" t="n" s="0">
-        <v>597.0</v>
+        <v>615.0</v>
       </c>
       <c r="E56" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="F56" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G56" t="b" s="0">
         <v>0</v>
@@ -2781,24 +2991,24 @@
         <v>1</v>
       </c>
       <c r="I56" t="n" s="0">
-        <v>536.532958984375</v>
+        <v>454.7370300292969</v>
       </c>
       <c r="J56" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B57" t="s" s="0">
         <v>169</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="C57" t="s" s="0">
         <v>170</v>
       </c>
-      <c r="C57" t="s" s="0">
-        <v>171</v>
-      </c>
       <c r="D57" t="n" s="0">
-        <v>609.0</v>
+        <v>615.0</v>
       </c>
       <c r="E57" t="n" s="0">
         <v>1.0</v>
@@ -2813,24 +3023,24 @@
         <v>1</v>
       </c>
       <c r="I57" t="n" s="0">
-        <v>255.2550048828125</v>
+        <v>458.68701171875</v>
       </c>
       <c r="J57" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B58" t="s" s="0">
         <v>172</v>
       </c>
-      <c r="B58" t="s" s="0">
+      <c r="C58" t="s" s="0">
         <v>173</v>
       </c>
-      <c r="C58" t="s" s="0">
-        <v>174</v>
-      </c>
       <c r="D58" t="n" s="0">
-        <v>609.0</v>
+        <v>614.0</v>
       </c>
       <c r="E58" t="n" s="0">
         <v>3.0</v>
@@ -2845,30 +3055,30 @@
         <v>1</v>
       </c>
       <c r="I58" t="n" s="0">
-        <v>309.2169494628906</v>
+        <v>474.2420959472656</v>
       </c>
       <c r="J58" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="B59" t="s" s="0">
+      <c r="C59" t="s" s="0">
         <v>176</v>
       </c>
-      <c r="C59" t="s" s="0">
-        <v>177</v>
-      </c>
       <c r="D59" t="n" s="0">
-        <v>102.0</v>
+        <v>615.0</v>
       </c>
       <c r="E59" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="F59" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G59" t="b" s="0">
         <v>0</v>
@@ -2877,30 +3087,30 @@
         <v>1</v>
       </c>
       <c r="I59" t="n" s="0">
-        <v>84.2820053100586</v>
+        <v>476.7940673828125</v>
       </c>
       <c r="J59" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B60" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="B60" t="s" s="0">
+      <c r="C60" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="C60" t="s" s="0">
-        <v>180</v>
-      </c>
       <c r="D60" t="n" s="0">
-        <v>583.0</v>
+        <v>614.0</v>
       </c>
       <c r="E60" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F60" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G60" t="b" s="0">
         <v>0</v>
@@ -2909,30 +3119,30 @@
         <v>1</v>
       </c>
       <c r="I60" t="n" s="0">
-        <v>615.0039672851562</v>
+        <v>466.552978515625</v>
       </c>
       <c r="J60" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="B61" t="s" s="0">
         <v>181</v>
       </c>
-      <c r="B61" t="s" s="0">
+      <c r="C61" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="C61" t="s" s="0">
-        <v>183</v>
-      </c>
       <c r="D61" t="n" s="0">
-        <v>102.0</v>
+        <v>615.0</v>
       </c>
       <c r="E61" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F61" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G61" t="b" s="0">
         <v>0</v>
@@ -2941,27 +3151,27 @@
         <v>1</v>
       </c>
       <c r="I61" t="n" s="0">
-        <v>101.04100036621094</v>
+        <v>457.72906494140625</v>
       </c>
       <c r="J61" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B62" t="s" s="0">
         <v>184</v>
       </c>
-      <c r="B62" t="s" s="0">
+      <c r="C62" t="s" s="0">
         <v>185</v>
       </c>
-      <c r="C62" t="s" s="0">
-        <v>186</v>
-      </c>
       <c r="D62" t="n" s="0">
-        <v>102.0</v>
+        <v>607.0</v>
       </c>
       <c r="E62" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F62" t="n" s="0">
         <v>1.0</v>
@@ -2973,30 +3183,30 @@
         <v>1</v>
       </c>
       <c r="I62" t="n" s="0">
-        <v>89.6290054321289</v>
+        <v>453.6310729980469</v>
       </c>
       <c r="J62" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="B63" t="s" s="0">
         <v>187</v>
       </c>
-      <c r="B63" t="s" s="0">
+      <c r="C63" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="C63" t="s" s="0">
-        <v>189</v>
-      </c>
       <c r="D63" t="n" s="0">
-        <v>102.0</v>
+        <v>614.0</v>
       </c>
       <c r="E63" t="n" s="0">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="F63" t="n" s="0">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G63" t="b" s="0">
         <v>0</v>
@@ -3005,24 +3215,24 @@
         <v>1</v>
       </c>
       <c r="I63" t="n" s="0">
-        <v>95.46599578857422</v>
+        <v>458.7789306640625</v>
       </c>
       <c r="J63" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="B64" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="B64" t="s" s="0">
+      <c r="C64" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="C64" t="s" s="0">
-        <v>192</v>
-      </c>
       <c r="D64" t="n" s="0">
-        <v>102.0</v>
+        <v>614.0</v>
       </c>
       <c r="E64" t="n" s="0">
         <v>1.0</v>
@@ -3037,30 +3247,30 @@
         <v>1</v>
       </c>
       <c r="I64" t="n" s="0">
-        <v>185.06900024414062</v>
+        <v>456.4159851074219</v>
       </c>
       <c r="J64" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="B65" t="s" s="0">
         <v>193</v>
       </c>
-      <c r="B65" t="s" s="0">
+      <c r="C65" t="s" s="0">
         <v>194</v>
       </c>
-      <c r="C65" t="s" s="0">
-        <v>195</v>
-      </c>
       <c r="D65" t="n" s="0">
-        <v>102.0</v>
+        <v>607.0</v>
       </c>
       <c r="E65" t="n" s="0">
-        <v>18.0</v>
+        <v>2.0</v>
       </c>
       <c r="F65" t="n" s="0">
-        <v>18.0</v>
+        <v>2.0</v>
       </c>
       <c r="G65" t="b" s="0">
         <v>0</v>
@@ -3069,24 +3279,24 @@
         <v>1</v>
       </c>
       <c r="I65" t="n" s="0">
-        <v>108.8489990234375</v>
+        <v>431.5380859375</v>
       </c>
       <c r="J65" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="B66" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="B66" t="s" s="0">
+      <c r="C66" t="s" s="0">
         <v>197</v>
       </c>
-      <c r="C66" t="s" s="0">
-        <v>198</v>
-      </c>
       <c r="D66" t="n" s="0">
-        <v>102.0</v>
+        <v>607.0</v>
       </c>
       <c r="E66" t="n" s="0">
         <v>6.0</v>
@@ -3101,30 +3311,30 @@
         <v>1</v>
       </c>
       <c r="I66" t="n" s="0">
-        <v>172.55398559570312</v>
+        <v>451.35198974609375</v>
       </c>
       <c r="J66" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="B67" t="s" s="0">
         <v>199</v>
       </c>
-      <c r="B67" t="s" s="0">
+      <c r="C67" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="C67" t="s" s="0">
-        <v>201</v>
-      </c>
       <c r="D67" t="n" s="0">
-        <v>610.0</v>
+        <v>614.0</v>
       </c>
       <c r="E67" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F67" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G67" t="b" s="0">
         <v>0</v>
@@ -3133,30 +3343,30 @@
         <v>1</v>
       </c>
       <c r="I67" t="n" s="0">
-        <v>272.3119812011719</v>
+        <v>451.27105712890625</v>
       </c>
       <c r="J67" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="B68" t="s" s="0">
         <v>202</v>
       </c>
-      <c r="B68" t="s" s="0">
+      <c r="C68" t="s" s="0">
         <v>203</v>
       </c>
-      <c r="C68" t="s" s="0">
-        <v>204</v>
-      </c>
       <c r="D68" t="n" s="0">
-        <v>102.0</v>
+        <v>614.0</v>
       </c>
       <c r="E68" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F68" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G68" t="b" s="0">
         <v>0</v>
@@ -3165,24 +3375,24 @@
         <v>1</v>
       </c>
       <c r="I68" t="n" s="0">
-        <v>102.52699279785156</v>
+        <v>451.5210876464844</v>
       </c>
       <c r="J68" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="B69" t="s" s="0">
         <v>205</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="C69" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="C69" t="s" s="0">
-        <v>207</v>
-      </c>
       <c r="D69" t="n" s="0">
-        <v>45.0</v>
+        <v>614.0</v>
       </c>
       <c r="E69" t="n" s="0">
         <v>1.0</v>
@@ -3197,24 +3407,24 @@
         <v>1</v>
       </c>
       <c r="I69" t="n" s="0">
-        <v>32.87699890136719</v>
+        <v>425.8459777832031</v>
       </c>
       <c r="J69" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="B70" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="B70" t="s" s="0">
+      <c r="C70" t="s" s="0">
         <v>209</v>
       </c>
-      <c r="C70" t="s" s="0">
-        <v>210</v>
-      </c>
       <c r="D70" t="n" s="0">
-        <v>609.0</v>
+        <v>607.0</v>
       </c>
       <c r="E70" t="n" s="0">
         <v>1.0</v>
@@ -3229,30 +3439,30 @@
         <v>1</v>
       </c>
       <c r="I70" t="n" s="0">
-        <v>425.7868957519531</v>
+        <v>462.3901062011719</v>
       </c>
       <c r="J70" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B71" t="s" s="0">
         <v>211</v>
       </c>
-      <c r="B71" t="s" s="0">
+      <c r="C71" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="C71" t="s" s="0">
-        <v>213</v>
-      </c>
       <c r="D71" t="n" s="0">
-        <v>102.0</v>
+        <v>614.0</v>
       </c>
       <c r="E71" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F71" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G71" t="b" s="0">
         <v>0</v>
@@ -3261,30 +3471,30 @@
         <v>1</v>
       </c>
       <c r="I71" t="n" s="0">
-        <v>75.61701202392578</v>
+        <v>441.7900085449219</v>
       </c>
       <c r="J71" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="B72" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="B72" t="s" s="0">
+      <c r="C72" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="C72" t="s" s="0">
-        <v>216</v>
-      </c>
       <c r="D72" t="n" s="0">
-        <v>598.0</v>
+        <v>607.0</v>
       </c>
       <c r="E72" t="n" s="0">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="F72" t="n" s="0">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G72" t="b" s="0">
         <v>0</v>
@@ -3293,30 +3503,30 @@
         <v>1</v>
       </c>
       <c r="I72" t="n" s="0">
-        <v>673.2310180664062</v>
+        <v>463.8749694824219</v>
       </c>
       <c r="J72" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="B73" t="s" s="0">
         <v>217</v>
       </c>
-      <c r="B73" t="s" s="0">
+      <c r="C73" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="C73" t="s" s="0">
-        <v>219</v>
-      </c>
       <c r="D73" t="n" s="0">
-        <v>610.0</v>
+        <v>607.0</v>
       </c>
       <c r="E73" t="n" s="0">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
       <c r="F73" t="n" s="0">
-        <v>8.0</v>
+        <v>18.0</v>
       </c>
       <c r="G73" t="b" s="0">
         <v>0</v>
@@ -3325,30 +3535,30 @@
         <v>1</v>
       </c>
       <c r="I73" t="n" s="0">
-        <v>293.74700927734375</v>
+        <v>452.21197509765625</v>
       </c>
       <c r="J73" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="B74" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="B74" t="s" s="0">
+      <c r="C74" t="s" s="0">
         <v>221</v>
       </c>
-      <c r="C74" t="s" s="0">
-        <v>222</v>
-      </c>
       <c r="D74" t="n" s="0">
-        <v>609.0</v>
+        <v>615.0</v>
       </c>
       <c r="E74" t="n" s="0">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="F74" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G74" t="b" s="0">
         <v>0</v>
@@ -3357,30 +3567,30 @@
         <v>1</v>
       </c>
       <c r="I74" t="n" s="0">
-        <v>567.6028442382812</v>
+        <v>450.5570068359375</v>
       </c>
       <c r="J74" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B75" t="s" s="0">
         <v>223</v>
       </c>
-      <c r="B75" t="s" s="0">
+      <c r="C75" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="C75" t="s" s="0">
-        <v>225</v>
-      </c>
       <c r="D75" t="n" s="0">
-        <v>1.0</v>
+        <v>54.0</v>
       </c>
       <c r="E75" t="n" s="0">
-        <v>35.0</v>
+        <v>1.0</v>
       </c>
       <c r="F75" t="n" s="0">
-        <v>35.0</v>
+        <v>1.0</v>
       </c>
       <c r="G75" t="b" s="0">
         <v>0</v>
@@ -3389,30 +3599,30 @@
         <v>1</v>
       </c>
       <c r="I75" t="n" s="0">
-        <v>0.28999999165534973</v>
+        <v>67.54199981689453</v>
       </c>
       <c r="J75" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="B76" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="B76" t="s" s="0">
-        <v>227</v>
-      </c>
       <c r="C76" t="s" s="0">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1.0</v>
+        <v>615.0</v>
       </c>
       <c r="E76" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F76" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G76" t="b" s="0">
         <v>0</v>
@@ -3421,30 +3631,30 @@
         <v>1</v>
       </c>
       <c r="I76" t="n" s="0">
-        <v>1.3700000047683716</v>
+        <v>452.0330810546875</v>
       </c>
       <c r="J76" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C77" t="s" s="0">
         <v>229</v>
       </c>
-      <c r="B77" t="s" s="0">
-        <v>230</v>
-      </c>
-      <c r="C77" t="s" s="0">
-        <v>231</v>
-      </c>
       <c r="D77" t="n" s="0">
-        <v>45.0</v>
+        <v>615.0</v>
       </c>
       <c r="E77" t="n" s="0">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="F77" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G77" t="b" s="0">
         <v>0</v>
@@ -3453,30 +3663,30 @@
         <v>1</v>
       </c>
       <c r="I77" t="n" s="0">
-        <v>31.016998291015625</v>
+        <v>451.2050476074219</v>
       </c>
       <c r="J77" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B78" t="s" s="0">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C78" t="s" s="0">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>633.0</v>
+        <v>54.0</v>
       </c>
       <c r="E78" t="n" s="0">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
       <c r="F78" t="n" s="0">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
       <c r="G78" t="b" s="0">
         <v>0</v>
@@ -3485,30 +3695,30 @@
         <v>1</v>
       </c>
       <c r="I78" t="n" s="0">
-        <v>587.2880249023438</v>
+        <v>53.59700012207031</v>
       </c>
       <c r="J78" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B79" t="s" s="0">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C79" t="s" s="0">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>655.0</v>
+        <v>1.0</v>
       </c>
       <c r="E79" t="n" s="0">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="F79" t="n" s="0">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="G79" t="b" s="0">
         <v>0</v>
@@ -3517,30 +3727,30 @@
         <v>1</v>
       </c>
       <c r="I79" t="n" s="0">
-        <v>589.7760009765625</v>
+        <v>0.1679999977350235</v>
       </c>
       <c r="J79" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B80" t="s" s="0">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C80" t="s" s="0">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>633.0</v>
+        <v>1.0</v>
       </c>
       <c r="E80" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F80" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G80" t="b" s="0">
         <v>0</v>
@@ -3549,30 +3759,30 @@
         <v>1</v>
       </c>
       <c r="I80" t="n" s="0">
-        <v>589.8490600585938</v>
+        <v>0.25200000405311584</v>
       </c>
       <c r="J80" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B81" t="s" s="0">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C81" t="s" s="0">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>610.0</v>
+        <v>156.0</v>
       </c>
       <c r="E81" t="n" s="0">
-        <v>2.0</v>
+        <v>27.0</v>
       </c>
       <c r="F81" t="n" s="0">
-        <v>2.0</v>
+        <v>24.0</v>
       </c>
       <c r="G81" t="b" s="0">
         <v>0</v>
@@ -3581,30 +3791,30 @@
         <v>1</v>
       </c>
       <c r="I81" t="n" s="0">
-        <v>439.3250427246094</v>
+        <v>218.85498046875</v>
       </c>
       <c r="J81" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s" s="0">
         <v>243</v>
       </c>
-      <c r="B82" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="C82" t="s" s="0">
-        <v>245</v>
-      </c>
       <c r="D82" t="n" s="0">
-        <v>609.0</v>
+        <v>54.0</v>
       </c>
       <c r="E82" t="n" s="0">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="F82" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G82" t="b" s="0">
         <v>0</v>
@@ -3613,30 +3823,30 @@
         <v>1</v>
       </c>
       <c r="I82" t="n" s="0">
-        <v>703.0579833984375</v>
+        <v>69.34200286865234</v>
       </c>
       <c r="J82" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="B83" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s" s="0">
         <v>246</v>
       </c>
-      <c r="C83" t="s" s="0">
-        <v>247</v>
-      </c>
       <c r="D83" t="n" s="0">
-        <v>45.0</v>
+        <v>607.0</v>
       </c>
       <c r="E83" t="n" s="0">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="F83" t="n" s="0">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
       <c r="G83" t="b" s="0">
         <v>0</v>
@@ -3645,24 +3855,24 @@
         <v>1</v>
       </c>
       <c r="I83" t="n" s="0">
-        <v>34.49100112915039</v>
+        <v>458.88397216796875</v>
       </c>
       <c r="J83" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B84" t="s" s="0">
         <v>248</v>
       </c>
-      <c r="B84" t="s" s="0">
+      <c r="C84" t="s" s="0">
         <v>249</v>
       </c>
-      <c r="C84" t="s" s="0">
-        <v>250</v>
-      </c>
       <c r="D84" t="n" s="0">
-        <v>102.0</v>
+        <v>615.0</v>
       </c>
       <c r="E84" t="n" s="0">
         <v>2.0</v>
@@ -3677,30 +3887,30 @@
         <v>1</v>
       </c>
       <c r="I84" t="n" s="0">
-        <v>172.23699951171875</v>
+        <v>464.6840515136719</v>
       </c>
       <c r="J84" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B85" t="s" s="0">
         <v>251</v>
       </c>
-      <c r="B85" t="s" s="0">
+      <c r="C85" t="s" s="0">
         <v>252</v>
       </c>
-      <c r="C85" t="s" s="0">
-        <v>253</v>
-      </c>
       <c r="D85" t="n" s="0">
-        <v>102.0</v>
+        <v>657.0</v>
       </c>
       <c r="E85" t="n" s="0">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="F85" t="n" s="0">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G85" t="b" s="0">
         <v>0</v>
@@ -3709,15 +3919,15 @@
         <v>1</v>
       </c>
       <c r="I85" t="n" s="0">
-        <v>81.0370101928711</v>
+        <v>550.5220336914062</v>
       </c>
       <c r="J85" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s" s="0">
         <v>254</v>
@@ -3726,13 +3936,13 @@
         <v>255</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>102.0</v>
+        <v>660.0</v>
       </c>
       <c r="E86" t="n" s="0">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="F86" t="n" s="0">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="G86" t="b" s="0">
         <v>0</v>
@@ -3741,30 +3951,30 @@
         <v>1</v>
       </c>
       <c r="I86" t="n" s="0">
-        <v>104.08100891113281</v>
+        <v>526.7689208984375</v>
       </c>
       <c r="J86" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="B87" t="s" s="0">
         <v>256</v>
       </c>
-      <c r="B87" t="s" s="0">
+      <c r="C87" t="s" s="0">
         <v>257</v>
       </c>
-      <c r="C87" t="s" s="0">
-        <v>258</v>
-      </c>
       <c r="D87" t="n" s="0">
-        <v>609.0</v>
+        <v>645.0</v>
       </c>
       <c r="E87" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F87" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G87" t="b" s="0">
         <v>0</v>
@@ -3773,30 +3983,30 @@
         <v>1</v>
       </c>
       <c r="I87" t="n" s="0">
-        <v>748.8020629882812</v>
+        <v>512.9849853515625</v>
       </c>
       <c r="J87" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="C88" t="s" s="0">
         <v>259</v>
       </c>
-      <c r="B88" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="C88" t="s" s="0">
-        <v>261</v>
-      </c>
       <c r="D88" t="n" s="0">
-        <v>1.0</v>
+        <v>156.0</v>
       </c>
       <c r="E88" t="n" s="0">
-        <v>6.0</v>
+        <v>27.0</v>
       </c>
       <c r="F88" t="n" s="0">
-        <v>6.0</v>
+        <v>27.0</v>
       </c>
       <c r="G88" t="b" s="0">
         <v>0</v>
@@ -3805,30 +4015,30 @@
         <v>1</v>
       </c>
       <c r="I88" t="n" s="0">
-        <v>0.20000000298023224</v>
+        <v>218.00601196289062</v>
       </c>
       <c r="J88" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="C89" t="s" s="0">
         <v>262</v>
       </c>
-      <c r="B89" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="C89" t="s" s="0">
-        <v>264</v>
-      </c>
       <c r="D89" t="n" s="0">
-        <v>633.0</v>
+        <v>607.0</v>
       </c>
       <c r="E89" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F89" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G89" t="b" s="0">
         <v>0</v>
@@ -3837,30 +4047,30 @@
         <v>1</v>
       </c>
       <c r="I89" t="n" s="0">
-        <v>567.2208862304688</v>
+        <v>456.3470458984375</v>
       </c>
       <c r="J89" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="C90" t="s" s="0">
         <v>265</v>
       </c>
-      <c r="B90" t="s" s="0">
-        <v>266</v>
-      </c>
-      <c r="C90" t="s" s="0">
-        <v>267</v>
-      </c>
       <c r="D90" t="n" s="0">
-        <v>102.0</v>
+        <v>645.0</v>
       </c>
       <c r="E90" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F90" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G90" t="b" s="0">
         <v>0</v>
@@ -3869,24 +4079,24 @@
         <v>1</v>
       </c>
       <c r="I90" t="n" s="0">
-        <v>101.78299713134766</v>
+        <v>499.7630310058594</v>
       </c>
       <c r="J90" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="C91" t="s" s="0">
         <v>268</v>
       </c>
-      <c r="B91" t="s" s="0">
-        <v>269</v>
-      </c>
-      <c r="C91" t="s" s="0">
-        <v>262</v>
-      </c>
       <c r="D91" t="n" s="0">
-        <v>650.0</v>
+        <v>645.0</v>
       </c>
       <c r="E91" t="n" s="0">
         <v>1.0</v>
@@ -3901,27 +4111,27 @@
         <v>1</v>
       </c>
       <c r="I91" t="n" s="0">
-        <v>541.0919799804688</v>
+        <v>530.4619140625</v>
       </c>
       <c r="J91" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="0">
+        <v>269</v>
+      </c>
+      <c r="B92" t="s" s="0">
         <v>270</v>
       </c>
-      <c r="B92" t="s" s="0">
+      <c r="C92" t="s" s="0">
         <v>271</v>
       </c>
-      <c r="C92" t="s" s="0">
-        <v>272</v>
-      </c>
       <c r="D92" t="n" s="0">
-        <v>610.0</v>
+        <v>607.0</v>
       </c>
       <c r="E92" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F92" t="n" s="0">
         <v>1.0</v>
@@ -3933,30 +4143,30 @@
         <v>1</v>
       </c>
       <c r="I92" t="n" s="0">
-        <v>670.5191040039062</v>
+        <v>467.2880554199219</v>
       </c>
       <c r="J92" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="B93" t="s" s="0">
         <v>273</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="C93" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="C93" t="s" s="0">
-        <v>275</v>
-      </c>
       <c r="D93" t="n" s="0">
-        <v>609.0</v>
+        <v>1.0</v>
       </c>
       <c r="E93" t="n" s="0">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="F93" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G93" t="b" s="0">
         <v>0</v>
@@ -3965,30 +4175,30 @@
         <v>1</v>
       </c>
       <c r="I93" t="n" s="0">
-        <v>245.5830535888672</v>
+        <v>0.6650000214576721</v>
       </c>
       <c r="J93" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="B94" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="B94" t="s" s="0">
+      <c r="C94" t="s" s="0">
         <v>277</v>
       </c>
-      <c r="C94" t="s" s="0">
-        <v>278</v>
-      </c>
       <c r="D94" t="n" s="0">
-        <v>633.0</v>
+        <v>607.0</v>
       </c>
       <c r="E94" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F94" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G94" t="b" s="0">
         <v>0</v>
@@ -3997,24 +4207,24 @@
         <v>1</v>
       </c>
       <c r="I94" t="n" s="0">
-        <v>542.9090576171875</v>
+        <v>452.9290771484375</v>
       </c>
       <c r="J94" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="B95" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="B95" t="s" s="0">
+      <c r="C95" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="C95" t="s" s="0">
-        <v>281</v>
-      </c>
       <c r="D95" t="n" s="0">
-        <v>633.0</v>
+        <v>645.0</v>
       </c>
       <c r="E95" t="n" s="0">
         <v>2.0</v>
@@ -4029,21 +4239,21 @@
         <v>1</v>
       </c>
       <c r="I95" t="n" s="0">
-        <v>459.3247985839844</v>
+        <v>516.51806640625</v>
       </c>
       <c r="J95" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="B96" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="B96" t="s" s="0">
+      <c r="C96" t="s" s="0">
         <v>283</v>
-      </c>
-      <c r="C96" t="s" s="0">
-        <v>284</v>
       </c>
       <c r="D96" t="n" s="0">
         <v>1.0</v>
@@ -4061,24 +4271,24 @@
         <v>1</v>
       </c>
       <c r="I96" t="n" s="0">
-        <v>0.5960000157356262</v>
+        <v>0.28700000047683716</v>
       </c>
       <c r="J96" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="B97" t="s" s="0">
         <v>285</v>
       </c>
-      <c r="B97" t="s" s="0">
+      <c r="C97" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="C97" t="s" s="0">
-        <v>287</v>
-      </c>
       <c r="D97" t="n" s="0">
-        <v>597.0</v>
+        <v>614.0</v>
       </c>
       <c r="E97" t="n" s="0">
         <v>1.0</v>
@@ -4093,30 +4303,30 @@
         <v>1</v>
       </c>
       <c r="I97" t="n" s="0">
-        <v>453.508056640625</v>
+        <v>416.0620422363281</v>
       </c>
       <c r="J97" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="0">
+        <v>287</v>
+      </c>
+      <c r="B98" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="B98" t="s" s="0">
+      <c r="C98" t="s" s="0">
         <v>289</v>
       </c>
-      <c r="C98" t="s" s="0">
-        <v>290</v>
-      </c>
       <c r="D98" t="n" s="0">
-        <v>152.0</v>
+        <v>645.0</v>
       </c>
       <c r="E98" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F98" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="b" s="0">
         <v>0</v>
@@ -4125,30 +4335,30 @@
         <v>1</v>
       </c>
       <c r="I98" t="n" s="0">
-        <v>129.37899780273438</v>
+        <v>526.5449829101562</v>
       </c>
       <c r="J98" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="0">
+        <v>290</v>
+      </c>
+      <c r="B99" t="s" s="0">
         <v>291</v>
       </c>
-      <c r="B99" t="s" s="0">
+      <c r="C99" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="C99" t="s" s="0">
-        <v>293</v>
-      </c>
       <c r="D99" t="n" s="0">
-        <v>1.0</v>
+        <v>606.0</v>
       </c>
       <c r="E99" t="n" s="0">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F99" t="n" s="0">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="G99" t="b" s="0">
         <v>0</v>
@@ -4157,30 +4367,30 @@
         <v>1</v>
       </c>
       <c r="I99" t="n" s="0">
-        <v>0.2540000081062317</v>
+        <v>431.8360595703125</v>
       </c>
       <c r="J99" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="0">
+        <v>293</v>
+      </c>
+      <c r="B100" t="s" s="0">
         <v>294</v>
       </c>
-      <c r="B100" t="s" s="0">
+      <c r="C100" t="s" s="0">
         <v>295</v>
       </c>
-      <c r="C100" t="s" s="0">
-        <v>296</v>
-      </c>
       <c r="D100" t="n" s="0">
-        <v>101.0</v>
+        <v>164.0</v>
       </c>
       <c r="E100" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F100" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G100" t="b" s="0">
         <v>0</v>
@@ -4189,30 +4399,30 @@
         <v>1</v>
       </c>
       <c r="I100" t="n" s="0">
-        <v>59.522003173828125</v>
+        <v>212.9219970703125</v>
       </c>
       <c r="J100" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="0">
+        <v>296</v>
+      </c>
+      <c r="B101" t="s" s="0">
         <v>297</v>
       </c>
-      <c r="B101" t="s" s="0">
+      <c r="C101" t="s" s="0">
         <v>298</v>
       </c>
-      <c r="C101" t="s" s="0">
-        <v>299</v>
-      </c>
       <c r="D101" t="n" s="0">
-        <v>93.0</v>
+        <v>156.0</v>
       </c>
       <c r="E101" t="n" s="0">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="F101" t="n" s="0">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="G101" t="b" s="0">
         <v>0</v>
@@ -4221,30 +4431,30 @@
         <v>1</v>
       </c>
       <c r="I101" t="n" s="0">
-        <v>76.5840072631836</v>
+        <v>212.37400817871094</v>
       </c>
       <c r="J101" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="0">
+        <v>299</v>
+      </c>
+      <c r="B102" t="s" s="0">
         <v>300</v>
       </c>
-      <c r="B102" t="s" s="0">
+      <c r="C102" t="s" s="0">
         <v>301</v>
       </c>
-      <c r="C102" t="s" s="0">
-        <v>302</v>
-      </c>
       <c r="D102" t="n" s="0">
-        <v>573.0</v>
+        <v>614.0</v>
       </c>
       <c r="E102" t="n" s="0">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="F102" t="n" s="0">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G102" t="b" s="0">
         <v>0</v>
@@ -4253,30 +4463,30 @@
         <v>1</v>
       </c>
       <c r="I102" t="n" s="0">
-        <v>268.8289794921875</v>
+        <v>422.4850769042969</v>
       </c>
       <c r="J102" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="B103" t="s" s="0">
         <v>303</v>
       </c>
-      <c r="B103" t="s" s="0">
+      <c r="C103" t="s" s="0">
         <v>304</v>
       </c>
-      <c r="C103" t="s" s="0">
-        <v>305</v>
-      </c>
       <c r="D103" t="n" s="0">
-        <v>87.0</v>
+        <v>1.0</v>
       </c>
       <c r="E103" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F103" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G103" t="b" s="0">
         <v>0</v>
@@ -4285,30 +4495,30 @@
         <v>1</v>
       </c>
       <c r="I103" t="n" s="0">
-        <v>62.61300277709961</v>
+        <v>0.45500001311302185</v>
       </c>
       <c r="J103" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="0">
+        <v>305</v>
+      </c>
+      <c r="B104" t="s" s="0">
         <v>306</v>
       </c>
-      <c r="B104" t="s" s="0">
+      <c r="C104" t="s" s="0">
         <v>307</v>
       </c>
-      <c r="C104" t="s" s="0">
-        <v>308</v>
-      </c>
       <c r="D104" t="n" s="0">
-        <v>87.0</v>
+        <v>156.0</v>
       </c>
       <c r="E104" t="n" s="0">
-        <v>13.0</v>
+        <v>5.0</v>
       </c>
       <c r="F104" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="G104" t="b" s="0">
         <v>0</v>
@@ -4317,42 +4527,810 @@
         <v>1</v>
       </c>
       <c r="I104" t="n" s="0">
-        <v>76.8169937133789</v>
+        <v>207.5030059814453</v>
       </c>
       <c r="J104" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="B105" t="s" s="0">
         <v>309</v>
       </c>
-      <c r="B105" t="s" s="0">
+      <c r="C105" t="s" s="0">
         <v>310</v>
       </c>
-      <c r="C105" t="s" s="0">
+      <c r="D105" t="n" s="0">
+        <v>606.0</v>
+      </c>
+      <c r="E105" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F105" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G105" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H105" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n" s="0">
+        <v>416.1949768066406</v>
+      </c>
+      <c r="J105" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
         <v>311</v>
       </c>
-      <c r="D105" t="n" s="0">
-        <v>609.0</v>
-      </c>
-      <c r="E105" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F105" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G105" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H105" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I105" t="n" s="0">
-        <v>456.69000244140625</v>
-      </c>
-      <c r="J105" t="b" s="0">
-        <v>1</v>
+      <c r="B106" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="D106" t="n" s="0">
+        <v>614.0</v>
+      </c>
+      <c r="E106" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F106" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G106" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H106" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n" s="0">
+        <v>418.5729064941406</v>
+      </c>
+      <c r="J106" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="D107" t="n" s="0">
+        <v>156.0</v>
+      </c>
+      <c r="E107" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F107" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G107" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H107" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n" s="0">
+        <v>226.9040069580078</v>
+      </c>
+      <c r="J107" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>318</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="D108" t="n" s="0">
+        <v>614.0</v>
+      </c>
+      <c r="E108" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F108" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="G108" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H108" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I108" t="n" s="0">
+        <v>448.093994140625</v>
+      </c>
+      <c r="J108" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="D109" t="n" s="0">
+        <v>614.0</v>
+      </c>
+      <c r="E109" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F109" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G109" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H109" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n" s="0">
+        <v>420.7860107421875</v>
+      </c>
+      <c r="J109" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="C110" t="s" s="0">
+        <v>325</v>
+      </c>
+      <c r="D110" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="E110" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F110" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G110" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H110" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I110" t="n" s="0">
+        <v>19.381000518798828</v>
+      </c>
+      <c r="J110" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="C111" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="D111" t="n" s="0">
+        <v>595.0</v>
+      </c>
+      <c r="E111" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F111" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G111" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H111" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n" s="0">
+        <v>443.31304931640625</v>
+      </c>
+      <c r="J111" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>331</v>
+      </c>
+      <c r="D112" t="n" s="0">
+        <v>593.0</v>
+      </c>
+      <c r="E112" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F112" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G112" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H112" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I112" t="n" s="0">
+        <v>413.0860595703125</v>
+      </c>
+      <c r="J112" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>332</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>334</v>
+      </c>
+      <c r="D113" t="n" s="0">
+        <v>605.0</v>
+      </c>
+      <c r="E113" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F113" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G113" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H113" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I113" t="n" s="0">
+        <v>412.9231262207031</v>
+      </c>
+      <c r="J113" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="D114" t="n" s="0">
+        <v>598.0</v>
+      </c>
+      <c r="E114" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F114" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G114" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H114" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n" s="0">
+        <v>399.91094970703125</v>
+      </c>
+      <c r="J114" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>338</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="D115" t="n" s="0">
+        <v>601.0</v>
+      </c>
+      <c r="E115" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F115" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G115" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H115" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I115" t="n" s="0">
+        <v>416.15093994140625</v>
+      </c>
+      <c r="J115" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>342</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="D116" t="n" s="0">
+        <v>138.0</v>
+      </c>
+      <c r="E116" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F116" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G116" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H116" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I116" t="n" s="0">
+        <v>164.66799926757812</v>
+      </c>
+      <c r="J116" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="D117" t="n" s="0">
+        <v>593.0</v>
+      </c>
+      <c r="E117" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F117" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G117" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H117" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n" s="0">
+        <v>357.43597412109375</v>
+      </c>
+      <c r="J117" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="D118" t="n" s="0">
+        <v>601.0</v>
+      </c>
+      <c r="E118" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F118" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G118" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H118" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n" s="0">
+        <v>369.3430480957031</v>
+      </c>
+      <c r="J118" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="D119" t="n" s="0">
+        <v>593.0</v>
+      </c>
+      <c r="E119" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F119" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G119" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H119" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n" s="0">
+        <v>338.1700134277344</v>
+      </c>
+      <c r="J119" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="D120" t="n" s="0">
+        <v>84.0</v>
+      </c>
+      <c r="E120" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F120" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="G120" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H120" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n" s="0">
+        <v>70.46300506591797</v>
+      </c>
+      <c r="J120" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="D121" t="n" s="0">
+        <v>499.0</v>
+      </c>
+      <c r="E121" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F121" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G121" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H121" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n" s="0">
+        <v>249.81602478027344</v>
+      </c>
+      <c r="J121" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="D122" t="n" s="0">
+        <v>473.0</v>
+      </c>
+      <c r="E122" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F122" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G122" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H122" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I122" t="n" s="0">
+        <v>202.38404846191406</v>
+      </c>
+      <c r="J122" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>362</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="D123" t="n" s="0">
+        <v>120.0</v>
+      </c>
+      <c r="E123" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F123" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G123" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H123" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I123" t="n" s="0">
+        <v>74.39000701904297</v>
+      </c>
+      <c r="J123" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>366</v>
+      </c>
+      <c r="D124" t="n" s="0">
+        <v>120.0</v>
+      </c>
+      <c r="E124" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F124" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G124" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H124" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I124" t="n" s="0">
+        <v>72.72799682617188</v>
+      </c>
+      <c r="J124" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>367</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>368</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>369</v>
+      </c>
+      <c r="D125" t="n" s="0">
+        <v>267.0</v>
+      </c>
+      <c r="E125" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F125" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G125" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H125" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I125" t="n" s="0">
+        <v>118.55098724365234</v>
+      </c>
+      <c r="J125" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>370</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>371</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>372</v>
+      </c>
+      <c r="D126" t="n" s="0">
+        <v>505.0</v>
+      </c>
+      <c r="E126" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F126" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G126" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H126" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I126" t="n" s="0">
+        <v>258.32098388671875</v>
+      </c>
+      <c r="J126" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>373</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>374</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>375</v>
+      </c>
+      <c r="D127" t="n" s="0">
+        <v>473.0</v>
+      </c>
+      <c r="E127" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F127" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G127" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H127" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I127" t="n" s="0">
+        <v>186.21600341796875</v>
+      </c>
+      <c r="J127" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>376</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>377</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>378</v>
+      </c>
+      <c r="D128" t="n" s="0">
+        <v>485.0</v>
+      </c>
+      <c r="E128" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F128" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G128" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H128" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n" s="0">
+        <v>245.343017578125</v>
+      </c>
+      <c r="J128" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>379</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>380</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>381</v>
+      </c>
+      <c r="D129" t="n" s="0">
+        <v>360.0</v>
+      </c>
+      <c r="E129" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F129" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G129" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H129" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n" s="0">
+        <v>374.2339782714844</v>
+      </c>
+      <c r="J129" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
